--- a/Simulation Survey Data/results-survey581821.xlsx
+++ b/Simulation Survey Data/results-survey581821.xlsx
@@ -107,7 +107,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:IV2"/>
+  <dimension ref="A1:IZ2"/>
   <cols>
     <col collapsed="false" hidden="false" max="1024" min="1" style="0" customWidth="false" width="11.5"/>
   </cols>
@@ -780,615 +780,635 @@
       </c>
       <c r="ED1" s="0" t="inlineStr">
         <is>
+          <t>EntfernPOI[BStel]</t>
+        </is>
+      </c>
+      <c r="EE1" s="0" t="inlineStr">
+        <is>
+          <t>EntfernPOI[InBew]</t>
+        </is>
+      </c>
+      <c r="EF1" s="0" t="inlineStr">
+        <is>
+          <t>EntfernPOI[OutBew]</t>
+        </is>
+      </c>
+      <c r="EG1" s="0" t="inlineStr">
+        <is>
           <t>PhoneSystem</t>
         </is>
       </c>
-      <c r="EE1" s="0" t="inlineStr">
+      <c r="EH1" s="0" t="inlineStr">
         <is>
           <t>PhoneSystem[other]</t>
         </is>
       </c>
-      <c r="EF1" s="0" t="inlineStr">
+      <c r="EI1" s="0" t="inlineStr">
         <is>
           <t>AppUseGeneral</t>
         </is>
       </c>
-      <c r="EG1" s="0" t="inlineStr">
+      <c r="EJ1" s="0" t="inlineStr">
         <is>
           <t>QualAppGeneral</t>
         </is>
       </c>
-      <c r="EH1" s="0" t="inlineStr">
+      <c r="EK1" s="0" t="inlineStr">
         <is>
           <t>AppUseStudy</t>
         </is>
       </c>
-      <c r="EI1" s="0" t="inlineStr">
+      <c r="EL1" s="0" t="inlineStr">
         <is>
           <t>AppUseDays</t>
         </is>
       </c>
-      <c r="EJ1" s="0" t="inlineStr">
+      <c r="EM1" s="0" t="inlineStr">
         <is>
           <t>TransferAppDetail</t>
         </is>
       </c>
-      <c r="EK1" s="0" t="inlineStr">
+      <c r="EN1" s="0" t="inlineStr">
         <is>
           <t>TAM[WA1]</t>
         </is>
       </c>
-      <c r="EL1" s="0" t="inlineStr">
+      <c r="EO1" s="0" t="inlineStr">
         <is>
           <t>TAM[WA2]</t>
         </is>
       </c>
-      <c r="EM1" s="0" t="inlineStr">
+      <c r="EP1" s="0" t="inlineStr">
         <is>
           <t>TAM[WA3]</t>
         </is>
       </c>
-      <c r="EN1" s="0" t="inlineStr">
+      <c r="EQ1" s="0" t="inlineStr">
         <is>
           <t>TAM[WN1]</t>
         </is>
       </c>
-      <c r="EO1" s="0" t="inlineStr">
+      <c r="ER1" s="0" t="inlineStr">
         <is>
           <t>TAM[WN2]</t>
         </is>
       </c>
-      <c r="EP1" s="0" t="inlineStr">
+      <c r="ES1" s="0" t="inlineStr">
         <is>
           <t>TAM[WN3]</t>
         </is>
       </c>
-      <c r="EQ1" s="0" t="inlineStr">
+      <c r="ET1" s="0" t="inlineStr">
         <is>
           <t>TAM[WN4]</t>
         </is>
       </c>
-      <c r="ER1" s="0" t="inlineStr">
+      <c r="EU1" s="0" t="inlineStr">
         <is>
           <t>TAM[WB1]</t>
         </is>
       </c>
-      <c r="ES1" s="0" t="inlineStr">
+      <c r="EV1" s="0" t="inlineStr">
         <is>
           <t>TAM[WB2]</t>
         </is>
       </c>
-      <c r="ET1" s="0" t="inlineStr">
+      <c r="EW1" s="0" t="inlineStr">
         <is>
           <t>TAM[WB3]</t>
         </is>
       </c>
-      <c r="EU1" s="0" t="inlineStr">
+      <c r="EX1" s="0" t="inlineStr">
         <is>
           <t>TAM[WB4]</t>
         </is>
       </c>
-      <c r="EV1" s="0" t="inlineStr">
+      <c r="EY1" s="0" t="inlineStr">
         <is>
           <t>TAM[WF1]</t>
         </is>
       </c>
-      <c r="EW1" s="0" t="inlineStr">
+      <c r="EZ1" s="0" t="inlineStr">
         <is>
           <t>TAM[WF2]</t>
         </is>
       </c>
-      <c r="EX1" s="0" t="inlineStr">
+      <c r="FA1" s="0" t="inlineStr">
         <is>
           <t>TAM[WF3]</t>
         </is>
       </c>
-      <c r="EY1" s="0" t="inlineStr">
+      <c r="FB1" s="0" t="inlineStr">
         <is>
           <t>TAM[WF4]</t>
         </is>
       </c>
-      <c r="EZ1" s="0" t="inlineStr">
+      <c r="FC1" s="0" t="inlineStr">
         <is>
           <t>TAM[WV1]</t>
         </is>
       </c>
-      <c r="FA1" s="0" t="inlineStr">
+      <c r="FD1" s="0" t="inlineStr">
         <is>
           <t>TAM[WV2]</t>
         </is>
       </c>
-      <c r="FB1" s="0" t="inlineStr">
+      <c r="FE1" s="0" t="inlineStr">
         <is>
           <t>TAM[WV3]</t>
         </is>
       </c>
-      <c r="FC1" s="0" t="inlineStr">
+      <c r="FF1" s="0" t="inlineStr">
         <is>
           <t>TAM[WV4]</t>
         </is>
       </c>
-      <c r="FD1" s="0" t="inlineStr">
+      <c r="FG1" s="0" t="inlineStr">
         <is>
           <t>TAM[NI1]</t>
         </is>
       </c>
-      <c r="FE1" s="0" t="inlineStr">
+      <c r="FH1" s="0" t="inlineStr">
         <is>
           <t>TAM[NI2]</t>
         </is>
       </c>
-      <c r="FF1" s="0" t="inlineStr">
+      <c r="FI1" s="0" t="inlineStr">
         <is>
           <t>TAM[NI3]</t>
         </is>
       </c>
-      <c r="FG1" s="0" t="inlineStr">
+      <c r="FJ1" s="0" t="inlineStr">
         <is>
           <t>TAM[NI4]</t>
         </is>
       </c>
-      <c r="FH1" s="0" t="inlineStr">
+      <c r="FK1" s="0" t="inlineStr">
         <is>
           <t>QualPos</t>
         </is>
       </c>
-      <c r="FI1" s="0" t="inlineStr">
+      <c r="FL1" s="0" t="inlineStr">
         <is>
           <t>QualNeg</t>
         </is>
       </c>
-      <c r="FJ1" s="0" t="inlineStr">
+      <c r="FM1" s="0" t="inlineStr">
         <is>
           <t>otherAppUse</t>
         </is>
       </c>
-      <c r="FK1" s="0" t="inlineStr">
+      <c r="FN1" s="0" t="inlineStr">
         <is>
           <t>QualOthApp</t>
         </is>
       </c>
-      <c r="FL1" s="0" t="inlineStr">
+      <c r="FO1" s="0" t="inlineStr">
         <is>
           <t>SystemLink</t>
         </is>
       </c>
-      <c r="FM1" s="0" t="inlineStr">
+      <c r="FP1" s="0" t="inlineStr">
         <is>
           <t>eMailIG</t>
         </is>
       </c>
-      <c r="FN1" s="0" t="inlineStr">
+      <c r="FQ1" s="0" t="inlineStr">
         <is>
           <t>eMailValidIG</t>
         </is>
       </c>
-      <c r="FO1" s="0" t="inlineStr">
+      <c r="FR1" s="0" t="inlineStr">
         <is>
           <t>eMailKG</t>
         </is>
       </c>
-      <c r="FP1" s="0" t="inlineStr">
+      <c r="FS1" s="0" t="inlineStr">
         <is>
           <t>eMailValidKG</t>
         </is>
       </c>
-      <c r="FQ1" s="0" t="inlineStr">
+      <c r="FT1" s="0" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="FR1" s="0" t="inlineStr">
+      <c r="FU1" s="0" t="inlineStr">
         <is>
           <t>interviewtime</t>
         </is>
       </c>
-      <c r="FS1" s="0" t="inlineStr">
+      <c r="FV1" s="0" t="inlineStr">
         <is>
           <t>groupTime19488</t>
         </is>
       </c>
-      <c r="FT1" s="0" t="inlineStr">
+      <c r="FW1" s="0" t="inlineStr">
         <is>
           <t>timePointTime</t>
         </is>
       </c>
-      <c r="FU1" s="0" t="inlineStr">
+      <c r="FX1" s="0" t="inlineStr">
         <is>
           <t>groupTime19449</t>
         </is>
       </c>
-      <c r="FV1" s="0" t="inlineStr">
+      <c r="FY1" s="0" t="inlineStr">
         <is>
           <t>EinvTime</t>
         </is>
       </c>
-      <c r="FW1" s="0" t="inlineStr">
+      <c r="FZ1" s="0" t="inlineStr">
         <is>
           <t>groupTime19489</t>
         </is>
       </c>
-      <c r="FX1" s="0" t="inlineStr">
+      <c r="GA1" s="0" t="inlineStr">
         <is>
           <t>randomGroupTime</t>
         </is>
       </c>
-      <c r="FY1" s="0" t="inlineStr">
+      <c r="GB1" s="0" t="inlineStr">
         <is>
           <t>studyGroupTime</t>
         </is>
       </c>
-      <c r="FZ1" s="0" t="inlineStr">
+      <c r="GC1" s="0" t="inlineStr">
         <is>
           <t>AppNameTime</t>
         </is>
       </c>
-      <c r="GA1" s="0" t="inlineStr">
+      <c r="GD1" s="0" t="inlineStr">
         <is>
           <t>groupTime19452</t>
         </is>
       </c>
-      <c r="GB1" s="0" t="inlineStr">
+      <c r="GE1" s="0" t="inlineStr">
         <is>
           <t>Bew1Time</t>
         </is>
       </c>
-      <c r="GC1" s="0" t="inlineStr">
+      <c r="GF1" s="0" t="inlineStr">
         <is>
           <t>Bew2Time</t>
         </is>
       </c>
-      <c r="GD1" s="0" t="inlineStr">
+      <c r="GG1" s="0" t="inlineStr">
         <is>
           <t>Bew3Time</t>
         </is>
       </c>
-      <c r="GE1" s="0" t="inlineStr">
+      <c r="GH1" s="0" t="inlineStr">
         <is>
           <t>Bew4Time</t>
         </is>
       </c>
-      <c r="GF1" s="0" t="inlineStr">
+      <c r="GI1" s="0" t="inlineStr">
         <is>
           <t>Bew5Time</t>
         </is>
       </c>
-      <c r="GG1" s="0" t="inlineStr">
+      <c r="GJ1" s="0" t="inlineStr">
         <is>
           <t>Bew6Time</t>
         </is>
       </c>
-      <c r="GH1" s="0" t="inlineStr">
+      <c r="GK1" s="0" t="inlineStr">
         <is>
           <t>STGTime</t>
         </is>
       </c>
-      <c r="GI1" s="0" t="inlineStr">
+      <c r="GL1" s="0" t="inlineStr">
         <is>
           <t>groupTime19451</t>
         </is>
       </c>
-      <c r="GJ1" s="0" t="inlineStr">
+      <c r="GM1" s="0" t="inlineStr">
         <is>
           <t>HabitTime</t>
         </is>
       </c>
-      <c r="GK1" s="0" t="inlineStr">
+      <c r="GN1" s="0" t="inlineStr">
         <is>
           <t>groupTime19453</t>
         </is>
       </c>
-      <c r="GL1" s="0" t="inlineStr">
+      <c r="GO1" s="0" t="inlineStr">
         <is>
           <t>Intention1Time</t>
         </is>
       </c>
-      <c r="GM1" s="0" t="inlineStr">
+      <c r="GP1" s="0" t="inlineStr">
         <is>
           <t>Intention2Time</t>
         </is>
       </c>
-      <c r="GN1" s="0" t="inlineStr">
+      <c r="GQ1" s="0" t="inlineStr">
         <is>
           <t>Intention3Time</t>
         </is>
       </c>
-      <c r="GO1" s="0" t="inlineStr">
+      <c r="GR1" s="0" t="inlineStr">
         <is>
           <t>groupTime19454</t>
         </is>
       </c>
-      <c r="GP1" s="0" t="inlineStr">
+      <c r="GS1" s="0" t="inlineStr">
         <is>
           <t>Att1Time</t>
         </is>
       </c>
-      <c r="GQ1" s="0" t="inlineStr">
+      <c r="GT1" s="0" t="inlineStr">
         <is>
           <t>Att2Time</t>
         </is>
       </c>
-      <c r="GR1" s="0" t="inlineStr">
+      <c r="GU1" s="0" t="inlineStr">
         <is>
           <t>Att3Time</t>
         </is>
       </c>
-      <c r="GS1" s="0" t="inlineStr">
+      <c r="GV1" s="0" t="inlineStr">
         <is>
           <t>Att4Time</t>
         </is>
       </c>
-      <c r="GT1" s="0" t="inlineStr">
+      <c r="GW1" s="0" t="inlineStr">
         <is>
           <t>Att5Time</t>
         </is>
       </c>
-      <c r="GU1" s="0" t="inlineStr">
+      <c r="GX1" s="0" t="inlineStr">
         <is>
           <t>groupTime19455</t>
         </is>
       </c>
-      <c r="GV1" s="0" t="inlineStr">
+      <c r="GY1" s="0" t="inlineStr">
         <is>
           <t>Norm1Time</t>
         </is>
       </c>
-      <c r="GW1" s="0" t="inlineStr">
+      <c r="GZ1" s="0" t="inlineStr">
         <is>
           <t>Norm2Time</t>
         </is>
       </c>
-      <c r="GX1" s="0" t="inlineStr">
+      <c r="HA1" s="0" t="inlineStr">
         <is>
           <t>Norm3Time</t>
         </is>
       </c>
-      <c r="GY1" s="0" t="inlineStr">
+      <c r="HB1" s="0" t="inlineStr">
         <is>
           <t>ACheck1Time</t>
         </is>
       </c>
-      <c r="GZ1" s="0" t="inlineStr">
+      <c r="HC1" s="0" t="inlineStr">
         <is>
           <t>Norm4Time</t>
         </is>
       </c>
-      <c r="HA1" s="0" t="inlineStr">
+      <c r="HD1" s="0" t="inlineStr">
         <is>
           <t>Norm5Time</t>
         </is>
       </c>
-      <c r="HB1" s="0" t="inlineStr">
+      <c r="HE1" s="0" t="inlineStr">
         <is>
           <t>Norm6Time</t>
         </is>
       </c>
-      <c r="HC1" s="0" t="inlineStr">
+      <c r="HF1" s="0" t="inlineStr">
         <is>
           <t>groupTime19456</t>
         </is>
       </c>
-      <c r="HD1" s="0" t="inlineStr">
+      <c r="HG1" s="0" t="inlineStr">
         <is>
           <t>Control1Time</t>
         </is>
       </c>
-      <c r="HE1" s="0" t="inlineStr">
+      <c r="HH1" s="0" t="inlineStr">
         <is>
           <t>Control2Time</t>
         </is>
       </c>
-      <c r="HF1" s="0" t="inlineStr">
+      <c r="HI1" s="0" t="inlineStr">
         <is>
           <t>Control3Time</t>
         </is>
       </c>
-      <c r="HG1" s="0" t="inlineStr">
+      <c r="HJ1" s="0" t="inlineStr">
         <is>
           <t>Control4Time</t>
         </is>
       </c>
-      <c r="HH1" s="0" t="inlineStr">
+      <c r="HK1" s="0" t="inlineStr">
         <is>
           <t>groupTime19458</t>
         </is>
       </c>
-      <c r="HI1" s="0" t="inlineStr">
+      <c r="HL1" s="0" t="inlineStr">
         <is>
           <t>KIMTime</t>
         </is>
       </c>
-      <c r="HJ1" s="0" t="inlineStr">
+      <c r="HM1" s="0" t="inlineStr">
         <is>
           <t>groupTime19461</t>
         </is>
       </c>
-      <c r="HK1" s="0" t="inlineStr">
+      <c r="HN1" s="0" t="inlineStr">
         <is>
           <t>ZiMoTime</t>
         </is>
       </c>
-      <c r="HL1" s="0" t="inlineStr">
+      <c r="HO1" s="0" t="inlineStr">
         <is>
           <t>groupTime19862</t>
         </is>
       </c>
-      <c r="HM1" s="0" t="inlineStr">
+      <c r="HP1" s="0" t="inlineStr">
         <is>
           <t>MotivCompTime</t>
         </is>
       </c>
-      <c r="HN1" s="0" t="inlineStr">
+      <c r="HQ1" s="0" t="inlineStr">
         <is>
           <t>groupTime19863</t>
         </is>
       </c>
-      <c r="HO1" s="0" t="inlineStr">
+      <c r="HR1" s="0" t="inlineStr">
         <is>
           <t>VolSelfTime</t>
         </is>
       </c>
-      <c r="HP1" s="0" t="inlineStr">
+      <c r="HS1" s="0" t="inlineStr">
         <is>
           <t>groupTime19864</t>
         </is>
       </c>
-      <c r="HQ1" s="0" t="inlineStr">
+      <c r="HT1" s="0" t="inlineStr">
         <is>
           <t>ActionPlanTime</t>
         </is>
       </c>
-      <c r="HR1" s="0" t="inlineStr">
+      <c r="HU1" s="0" t="inlineStr">
         <is>
           <t>groupTime19450</t>
         </is>
       </c>
-      <c r="HS1" s="0" t="inlineStr">
+      <c r="HV1" s="0" t="inlineStr">
         <is>
           <t>GebTime</t>
         </is>
       </c>
-      <c r="HT1" s="0" t="inlineStr">
+      <c r="HW1" s="0" t="inlineStr">
         <is>
           <t>GesTime</t>
         </is>
       </c>
-      <c r="HU1" s="0" t="inlineStr">
+      <c r="HX1" s="0" t="inlineStr">
         <is>
           <t>EthnTime</t>
         </is>
       </c>
-      <c r="HV1" s="0" t="inlineStr">
+      <c r="HY1" s="0" t="inlineStr">
         <is>
           <t>WohnTime</t>
         </is>
       </c>
-      <c r="HW1" s="0" t="inlineStr">
+      <c r="HZ1" s="0" t="inlineStr">
         <is>
           <t>EduTime</t>
         </is>
       </c>
-      <c r="HX1" s="0" t="inlineStr">
+      <c r="IA1" s="0" t="inlineStr">
         <is>
           <t>ProfTime</t>
         </is>
       </c>
-      <c r="HY1" s="0" t="inlineStr">
+      <c r="IB1" s="0" t="inlineStr">
         <is>
           <t>EinkoTime</t>
         </is>
       </c>
-      <c r="HZ1" s="0" t="inlineStr">
+      <c r="IC1" s="0" t="inlineStr">
         <is>
           <t>BrancheTime</t>
         </is>
       </c>
-      <c r="IA1" s="0" t="inlineStr">
+      <c r="ID1" s="0" t="inlineStr">
         <is>
           <t>AlltagAblTime</t>
         </is>
       </c>
-      <c r="IB1" s="0" t="inlineStr">
+      <c r="IE1" s="0" t="inlineStr">
+        <is>
+          <t>EntfernPOITime</t>
+        </is>
+      </c>
+      <c r="IF1" s="0" t="inlineStr">
         <is>
           <t>PhoneSystemTime</t>
         </is>
       </c>
-      <c r="IC1" s="0" t="inlineStr">
+      <c r="IG1" s="0" t="inlineStr">
         <is>
           <t>AppUseGeneralTime</t>
         </is>
       </c>
-      <c r="ID1" s="0" t="inlineStr">
+      <c r="IH1" s="0" t="inlineStr">
         <is>
           <t>QualAppGeneralTime</t>
         </is>
       </c>
-      <c r="IE1" s="0" t="inlineStr">
+      <c r="II1" s="0" t="inlineStr">
         <is>
           <t>groupTime19487</t>
         </is>
       </c>
-      <c r="IF1" s="0" t="inlineStr">
+      <c r="IJ1" s="0" t="inlineStr">
         <is>
           <t>AppUseStudyTime</t>
         </is>
       </c>
-      <c r="IG1" s="0" t="inlineStr">
+      <c r="IK1" s="0" t="inlineStr">
         <is>
           <t>AppUseDaysTime</t>
         </is>
       </c>
-      <c r="IH1" s="0" t="inlineStr">
+      <c r="IL1" s="0" t="inlineStr">
         <is>
           <t>TransferAppDetailTime</t>
         </is>
       </c>
-      <c r="II1" s="0" t="inlineStr">
+      <c r="IM1" s="0" t="inlineStr">
         <is>
           <t>groupTime19486</t>
         </is>
       </c>
-      <c r="IJ1" s="0" t="inlineStr">
+      <c r="IN1" s="0" t="inlineStr">
         <is>
           <t>TAMTime</t>
         </is>
       </c>
-      <c r="IK1" s="0" t="inlineStr">
+      <c r="IO1" s="0" t="inlineStr">
         <is>
           <t>QualPosTime</t>
         </is>
       </c>
-      <c r="IL1" s="0" t="inlineStr">
+      <c r="IP1" s="0" t="inlineStr">
         <is>
           <t>QualNegTime</t>
         </is>
       </c>
-      <c r="IM1" s="0" t="inlineStr">
+      <c r="IQ1" s="0" t="inlineStr">
         <is>
           <t>groupTime19491</t>
         </is>
       </c>
-      <c r="IN1" s="0" t="inlineStr">
+      <c r="IR1" s="0" t="inlineStr">
         <is>
           <t>otherAppUseTime</t>
         </is>
       </c>
-      <c r="IO1" s="0" t="inlineStr">
+      <c r="IS1" s="0" t="inlineStr">
         <is>
           <t>QualOthAppTime</t>
         </is>
       </c>
-      <c r="IP1" s="0" t="inlineStr">
+      <c r="IT1" s="0" t="inlineStr">
         <is>
           <t>groupTime19462</t>
         </is>
       </c>
-      <c r="IQ1" s="0" t="inlineStr">
+      <c r="IU1" s="0" t="inlineStr">
         <is>
           <t>SystemLinkTime</t>
         </is>
       </c>
-      <c r="IR1" s="0" t="inlineStr">
+      <c r="IV1" s="0" t="inlineStr">
         <is>
           <t>eMailIGTime</t>
         </is>
       </c>
-      <c r="IS1" s="0" t="inlineStr">
+      <c r="IW1" s="0" t="inlineStr">
         <is>
           <t>eMailValidIGTime</t>
         </is>
       </c>
-      <c r="IT1" s="0" t="inlineStr">
+      <c r="IX1" s="0" t="inlineStr">
         <is>
           <t>eMailKGTime</t>
         </is>
       </c>
-      <c r="IU1" s="0" t="inlineStr">
+      <c r="IY1" s="0" t="inlineStr">
         <is>
           <t>eMailValidKGTime</t>
         </is>
       </c>
-      <c r="IV1" s="0" t="inlineStr">
+      <c r="IZ1" s="0" t="inlineStr">
         <is>
           <t>NameTime</t>
         </is>
@@ -1396,11 +1416,11 @@
     </row>
     <row collapsed="false" customFormat="false" customHeight="false" hidden="false" ht="12.1" outlineLevel="0" r="2">
       <c r="A2" s="0" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>2026-03-24 09:55:00</t>
+          <t>2026-04-09 16:11:26</t>
         </is>
       </c>
       <c r="C2" s="0" t="n">
@@ -1412,16 +1432,16 @@
         </is>
       </c>
       <c r="E2" s="0" t="n">
-        <v>598916058</v>
+        <v>528927893</v>
       </c>
       <c r="F2" s="0" t="inlineStr">
         <is>
-          <t>2026-03-24 09:52:21</t>
+          <t>2026-04-09 16:04:50</t>
         </is>
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
-          <t>2026-03-24 09:55:00</t>
+          <t>2026-04-09 16:11:26</t>
         </is>
       </c>
       <c r="H2" s="0"/>
@@ -1446,91 +1466,85 @@
       </c>
       <c r="N2" s="0" t="inlineStr">
         <is>
-          <t>3 Tage</t>
+          <t>1 Tag</t>
         </is>
       </c>
       <c r="O2" s="0" t="n">
-        <v>532</v>
+        <v>56</v>
       </c>
       <c r="P2" s="0" t="inlineStr">
         <is>
-          <t>3 Tage</t>
+          <t>4 Tage</t>
         </is>
       </c>
       <c r="Q2" s="0" t="n">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="R2" s="0" t="inlineStr">
         <is>
-          <t>2 Tage</t>
+          <t>4 Tage</t>
         </is>
       </c>
       <c r="S2" s="0" t="n">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="T2" s="0" t="inlineStr">
         <is>
           <t>Nein, aber ich plane in den nächsten 30 Tagen mit regelmässiger körperlicher Aktivität zu starten.</t>
         </is>
       </c>
-      <c r="U2" s="0" t="n">
+      <c r="U2" s="0" t="inlineStr">
+        <is>
+          <t>3 </t>
+        </is>
+      </c>
+      <c r="V2" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="W2" s="0" t="inlineStr">
+        <is>
+          <t>3 </t>
+        </is>
+      </c>
+      <c r="X2" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y2" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="V2" s="0" t="inlineStr">
-        <is>
-          <t>2 </t>
-        </is>
-      </c>
-      <c r="W2" s="0" t="n">
+      <c r="Z2" s="0" t="inlineStr">
+        <is>
+          <t>3 </t>
+        </is>
+      </c>
+      <c r="AA2" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB2" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="X2" s="0" t="inlineStr">
-        <is>
-          <t>3 </t>
-        </is>
-      </c>
-      <c r="Y2" s="0" t="inlineStr">
-        <is>
-          <t>3 </t>
-        </is>
-      </c>
-      <c r="Z2" s="0" t="n">
+      <c r="AC2" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD2" s="0" t="n">
         <v>5</v>
-      </c>
-      <c r="AA2" s="0" t="inlineStr">
-        <is>
-          <t>3 </t>
-        </is>
-      </c>
-      <c r="AB2" s="0" t="inlineStr">
-        <is>
-          <t>3 </t>
-        </is>
-      </c>
-      <c r="AC2" s="0" t="inlineStr">
-        <is>
-          <t>3 </t>
-        </is>
-      </c>
-      <c r="AD2" s="0" t="n">
-        <v>4</v>
       </c>
       <c r="AE2" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="AF2" s="0" t="n">
+      <c r="AF2" s="0" t="inlineStr">
+        <is>
+          <t>3 </t>
+        </is>
+      </c>
+      <c r="AG2" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="AG2" s="0" t="inlineStr">
-        <is>
-          <t>3 </t>
-        </is>
-      </c>
       <c r="AH2" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI2" s="0" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ2" s="0" t="inlineStr">
         <is>
@@ -1541,177 +1555,161 @@
         <v>5</v>
       </c>
       <c r="AL2" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM2" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="AM2" s="0" t="inlineStr">
-        <is>
-          <t>3 </t>
-        </is>
-      </c>
       <c r="AN2" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO2" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP2" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ2" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="AO2" s="0" t="inlineStr">
-        <is>
-          <t>2 </t>
-        </is>
-      </c>
-      <c r="AP2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ2" s="0" t="inlineStr">
-        <is>
-          <t>3 </t>
-        </is>
-      </c>
       <c r="AR2" s="0" t="inlineStr">
         <is>
+          <t>4 - stimmt völlig</t>
+        </is>
+      </c>
+      <c r="AS2" s="0" t="inlineStr">
+        <is>
+          <t>2 - stimmt teils-teils</t>
+        </is>
+      </c>
+      <c r="AT2" s="0" t="inlineStr">
+        <is>
+          <t>0 - stimmt gar nicht</t>
+        </is>
+      </c>
+      <c r="AU2" s="0" t="inlineStr">
+        <is>
+          <t>2 - stimmt teils-teils</t>
+        </is>
+      </c>
+      <c r="AV2" s="0" t="inlineStr">
+        <is>
+          <t>4 - stimmt völlig</t>
+        </is>
+      </c>
+      <c r="AW2" s="0" t="inlineStr">
+        <is>
+          <t>2 - stimmt teils-teils</t>
+        </is>
+      </c>
+      <c r="AX2" s="0" t="inlineStr">
+        <is>
+          <t>2 - stimmt teils-teils</t>
+        </is>
+      </c>
+      <c r="AY2" s="0" t="inlineStr">
+        <is>
           <t>3 - stimmt ziemlich</t>
         </is>
       </c>
-      <c r="AS2" s="0" t="inlineStr">
+      <c r="AZ2" s="0" t="inlineStr">
+        <is>
+          <t>2 - stimmt teils-teils</t>
+        </is>
+      </c>
+      <c r="BA2" s="0" t="inlineStr">
+        <is>
+          <t>2 - stimmt teils-teils</t>
+        </is>
+      </c>
+      <c r="BB2" s="0" t="inlineStr">
         <is>
           <t>1 - stimmt wenig</t>
         </is>
       </c>
-      <c r="AT2" s="0" t="inlineStr">
-        <is>
-          <t>1 - stimmt wenig</t>
-        </is>
-      </c>
-      <c r="AU2" s="0" t="inlineStr">
-        <is>
-          <t>2 - stimmt teils-teils</t>
-        </is>
-      </c>
-      <c r="AV2" s="0" t="inlineStr">
-        <is>
-          <t>2 - stimmt teils-teils</t>
-        </is>
-      </c>
-      <c r="AW2" s="0" t="inlineStr">
-        <is>
-          <t>2 - stimmt teils-teils</t>
-        </is>
-      </c>
-      <c r="AX2" s="0" t="inlineStr">
-        <is>
-          <t>2 - stimmt teils-teils</t>
-        </is>
-      </c>
-      <c r="AY2" s="0" t="inlineStr">
+      <c r="BC2" s="0" t="inlineStr">
+        <is>
+          <t>4 - stimmt völlig</t>
+        </is>
+      </c>
+      <c r="BD2" s="0" t="inlineStr">
         <is>
           <t>3 - stimmt ziemlich</t>
         </is>
       </c>
-      <c r="AZ2" s="0" t="inlineStr">
-        <is>
-          <t>3 - stimmt ziemlich</t>
-        </is>
-      </c>
-      <c r="BA2" s="0" t="inlineStr">
-        <is>
-          <t>1 - stimmt wenig</t>
-        </is>
-      </c>
-      <c r="BB2" s="0" t="inlineStr">
-        <is>
-          <t>3 - stimmt ziemlich</t>
-        </is>
-      </c>
-      <c r="BC2" s="0" t="inlineStr">
-        <is>
-          <t>1 - stimmt wenig</t>
-        </is>
-      </c>
-      <c r="BD2" s="0" t="inlineStr">
-        <is>
-          <t>3 - stimmt ziemlich</t>
-        </is>
-      </c>
-      <c r="BE2" s="0" t="inlineStr">
+      <c r="BE2" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF2" s="0" t="inlineStr">
         <is>
           <t>4 </t>
         </is>
       </c>
-      <c r="BF2" s="0" t="inlineStr">
+      <c r="BG2" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH2" s="0" t="inlineStr">
         <is>
           <t>4 </t>
         </is>
       </c>
-      <c r="BG2" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH2" s="0" t="inlineStr">
-        <is>
-          <t>4 </t>
-        </is>
-      </c>
-      <c r="BI2" s="0" t="inlineStr">
-        <is>
-          <t>4 </t>
-        </is>
-      </c>
-      <c r="BJ2" s="0" t="inlineStr">
-        <is>
-          <t>4 </t>
-        </is>
-      </c>
-      <c r="BK2" s="0" t="inlineStr">
-        <is>
-          <t>1    ich stimme überhaupt nicht zu</t>
-        </is>
+      <c r="BI2" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ2" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK2" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="BL2" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="BM2" s="0" t="inlineStr">
+      <c r="BM2" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN2" s="0" t="inlineStr">
         <is>
           <t>4 </t>
-        </is>
-      </c>
-      <c r="BN2" s="0" t="inlineStr">
-        <is>
-          <t>1    ich stimme überhaupt nicht zu</t>
         </is>
       </c>
       <c r="BO2" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="BP2" s="0" t="n">
+      <c r="BP2" s="0" t="inlineStr">
+        <is>
+          <t>4 </t>
+        </is>
+      </c>
+      <c r="BQ2" s="0" t="inlineStr">
+        <is>
+          <t>5    ich stimme voll und ganz zu</t>
+        </is>
+      </c>
+      <c r="BR2" s="0" t="inlineStr">
+        <is>
+          <t>1    ich stimme überhaupt nicht zu</t>
+        </is>
+      </c>
+      <c r="BS2" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="BQ2" s="0" t="n">
+      <c r="BT2" s="0" t="inlineStr">
+        <is>
+          <t>4 </t>
+        </is>
+      </c>
+      <c r="BU2" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="BR2" s="0" t="inlineStr">
-        <is>
-          <t>1    ich stimme überhaupt nicht zu</t>
-        </is>
-      </c>
-      <c r="BS2" s="0" t="inlineStr">
+      <c r="BV2" s="0" t="inlineStr">
+        <is>
+          <t>5    ich stimme voll und ganz zu</t>
+        </is>
+      </c>
+      <c r="BW2" s="0" t="inlineStr">
         <is>
           <t>4 </t>
-        </is>
-      </c>
-      <c r="BT2" s="0" t="inlineStr">
-        <is>
-          <t>4 </t>
-        </is>
-      </c>
-      <c r="BU2" s="0" t="inlineStr">
-        <is>
-          <t>4 </t>
-        </is>
-      </c>
-      <c r="BV2" s="0" t="inlineStr">
-        <is>
-          <t>4 </t>
-        </is>
-      </c>
-      <c r="BW2" s="0" t="inlineStr">
-        <is>
-          <t>5    ich stimme voll und ganz zu</t>
         </is>
       </c>
       <c r="BX2" s="0" t="n">
@@ -1729,33 +1727,31 @@
         <v>3</v>
       </c>
       <c r="CB2" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CC2" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="CD2" s="0" t="inlineStr">
-        <is>
-          <t>4 </t>
-        </is>
+      <c r="CD2" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="CE2" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF2" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="CF2" s="0" t="n">
+      <c r="CG2" s="0" t="inlineStr">
+        <is>
+          <t>5    ich stimme voll und ganz zu</t>
+        </is>
+      </c>
+      <c r="CH2" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI2" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="CG2" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="CH2" s="0" t="inlineStr">
-        <is>
-          <t>1    ich stimme überhaupt nicht zu</t>
-        </is>
-      </c>
-      <c r="CI2" s="0" t="n">
-        <v>3</v>
-      </c>
       <c r="CJ2" s="0" t="inlineStr">
         <is>
           <t>3 </t>
@@ -1763,51 +1759,49 @@
       </c>
       <c r="CK2" s="0" t="inlineStr">
         <is>
+          <t>1     trifft nicht zu</t>
+        </is>
+      </c>
+      <c r="CL2" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="CM2" s="0" t="inlineStr">
+        <is>
+          <t>3 </t>
+        </is>
+      </c>
+      <c r="CN2" s="0" t="inlineStr">
+        <is>
           <t>2 </t>
         </is>
       </c>
-      <c r="CL2" s="0" t="inlineStr">
+      <c r="CO2" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="CP2" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="CQ2" s="0" t="inlineStr">
         <is>
           <t>3 </t>
         </is>
       </c>
-      <c r="CM2" s="0" t="inlineStr">
+      <c r="CR2" s="0" t="inlineStr">
         <is>
           <t>3 </t>
         </is>
       </c>
-      <c r="CN2" s="0" t="n">
+      <c r="CS2" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="CO2" s="0" t="inlineStr">
+      <c r="CT2" s="0" t="inlineStr">
         <is>
           <t>2 </t>
         </is>
       </c>
-      <c r="CP2" s="0" t="inlineStr">
-        <is>
-          <t>3 </t>
-        </is>
-      </c>
-      <c r="CQ2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="CR2" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="CS2" s="0" t="inlineStr">
-        <is>
-          <t>3 </t>
-        </is>
-      </c>
-      <c r="CT2" s="0" t="inlineStr">
-        <is>
-          <t>3 </t>
-        </is>
-      </c>
       <c r="CU2" s="0" t="inlineStr">
         <is>
-          <t>2008-03-05 00:00:00</t>
+          <t>2000-03-31 00:00:00</t>
         </is>
       </c>
       <c r="CV2" s="0" t="inlineStr">
@@ -1830,13 +1824,13 @@
       <c r="DA2" s="0"/>
       <c r="DB2" s="0" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nein</t>
         </is>
       </c>
       <c r="DC2" s="0"/>
       <c r="DD2" s="0" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="DE2" s="0"/>
@@ -1879,75 +1873,81 @@
       </c>
       <c r="DS2" s="0" t="inlineStr">
         <is>
-          <t>Selbständig</t>
+          <t>Studium</t>
         </is>
       </c>
       <c r="DT2" s="0"/>
       <c r="DU2" s="0" t="inlineStr">
         <is>
-          <t>4500-5000 CHF</t>
+          <t>1000 - 1500 CHF</t>
         </is>
       </c>
       <c r="DV2" s="0"/>
       <c r="DW2" s="0" t="inlineStr">
         <is>
-          <t>Bürojob sitzend</t>
+          <t>Bürojob oft sitzend</t>
         </is>
       </c>
       <c r="DX2" s="0" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="DY2" s="0" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="DZ2" s="0" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="EA2" s="0" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="EB2" s="0" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="EC2" s="0" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="ED2" s="0" t="inlineStr">
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="ED2" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="EE2" s="0" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="EF2" s="0" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="EG2" s="0" t="inlineStr">
         <is>
           <t>Android</t>
         </is>
       </c>
-      <c r="EE2" s="0"/>
-      <c r="EF2" s="0" t="inlineStr">
+      <c r="EH2" s="0"/>
+      <c r="EI2" s="0" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="EG2" s="0" t="inlineStr">
-        <is>
-          <t>Samsung Watch</t>
-        </is>
-      </c>
-      <c r="EH2" s="0" t="inlineStr">
+      <c r="EJ2" s="0" t="inlineStr">
+        <is>
+          <t>Oura Ring</t>
+        </is>
+      </c>
+      <c r="EK2" s="0" t="inlineStr">
         <is>
           <t>N. v.</t>
         </is>
       </c>
-      <c r="EI2" s="0"/>
-      <c r="EJ2" s="0"/>
-      <c r="EK2" s="0"/>
       <c r="EL2" s="0"/>
       <c r="EM2" s="0"/>
       <c r="EN2" s="0"/>
@@ -1972,118 +1972,118 @@
       <c r="FG2" s="0"/>
       <c r="FH2" s="0"/>
       <c r="FI2" s="0"/>
-      <c r="FJ2" s="0" t="inlineStr">
+      <c r="FJ2" s="0"/>
+      <c r="FK2" s="0"/>
+      <c r="FL2" s="0"/>
+      <c r="FM2" s="0" t="inlineStr">
         <is>
           <t>N. v.</t>
         </is>
       </c>
-      <c r="FK2" s="0"/>
-      <c r="FL2" s="0" t="inlineStr">
+      <c r="FN2" s="0"/>
+      <c r="FO2" s="0" t="inlineStr">
         <is>
           <t>if(timePoint == 1,   if(PhoneSystem == "Googl", "Android: https://play.google.com/store/apps/details?id=ai.gymian.alife",    if(PhoneSystem == "Apple", "iOS: https://apps.apple.com/ch/app/alife-dein-ki-coach/id6756587565", "Android: https://play.google.com/store/apps/details?id=ai.gymian.alife | iOS: https://apps.apple.com/ch/app/alife-dein-ki-coach/id6756587565"   )  ),   if(TOKEN:ATTRIBUTE_2 == "Googl", "Android: https://play.google.com/store/apps/details?id=ai.gymian.alife",    if(TOKEN:ATTRIBUTE_2 == "Apple", "iOS: https://apps.apple.com/ch/app/alife-dein-ki-coach/id6756587565", "Android: https://play.google.com/store/apps/details?id=ai.gymian.alife | iOS: https://apps.apple.com/ch/app/alife-dein-ki-coach/id6756587565"   )  ) )</t>
         </is>
       </c>
-      <c r="FM2" s="0" t="inlineStr">
-        <is>
-          <t>test@test.ch</t>
-        </is>
-      </c>
-      <c r="FN2" s="0" t="inlineStr">
-        <is>
-          <t>test@test.ch</t>
-        </is>
-      </c>
-      <c r="FO2" s="0"/>
-      <c r="FP2" s="0"/>
+      <c r="FP2" s="0" t="inlineStr">
+        <is>
+          <t>peter.meier@gmx.ch</t>
+        </is>
+      </c>
       <c r="FQ2" s="0" t="inlineStr">
         <is>
-          <t>Peter</t>
-        </is>
-      </c>
-      <c r="FR2" s="0" t="n">
-        <v>166.85</v>
-      </c>
+          <t>peter.meier@gmx.ch</t>
+        </is>
+      </c>
+      <c r="FR2" s="0"/>
       <c r="FS2" s="0"/>
-      <c r="FT2" s="0"/>
+      <c r="FT2" s="0" t="inlineStr">
+        <is>
+          <t>peter4573x</t>
+        </is>
+      </c>
       <c r="FU2" s="0" t="n">
-        <v>3.3</v>
+        <v>404.16</v>
       </c>
       <c r="FV2" s="0"/>
       <c r="FW2" s="0"/>
-      <c r="FX2" s="0"/>
+      <c r="FX2" s="0" t="n">
+        <v>6.1</v>
+      </c>
       <c r="FY2" s="0"/>
       <c r="FZ2" s="0"/>
-      <c r="GA2" s="0" t="n">
-        <v>11.48</v>
-      </c>
+      <c r="GA2" s="0"/>
       <c r="GB2" s="0"/>
       <c r="GC2" s="0"/>
-      <c r="GD2" s="0"/>
+      <c r="GD2" s="0" t="n">
+        <v>25.9</v>
+      </c>
       <c r="GE2" s="0"/>
       <c r="GF2" s="0"/>
       <c r="GG2" s="0"/>
       <c r="GH2" s="0"/>
-      <c r="GI2" s="0" t="n">
-        <v>5.39</v>
-      </c>
+      <c r="GI2" s="0"/>
       <c r="GJ2" s="0"/>
-      <c r="GK2" s="0" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="GL2" s="0"/>
+      <c r="GK2" s="0"/>
+      <c r="GL2" s="0" t="n">
+        <v>7.63</v>
+      </c>
       <c r="GM2" s="0"/>
-      <c r="GN2" s="0"/>
-      <c r="GO2" s="0" t="n">
-        <v>7.39</v>
-      </c>
+      <c r="GN2" s="0" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="GO2" s="0"/>
       <c r="GP2" s="0"/>
       <c r="GQ2" s="0"/>
-      <c r="GR2" s="0"/>
+      <c r="GR2" s="0" t="n">
+        <v>8.61</v>
+      </c>
       <c r="GS2" s="0"/>
       <c r="GT2" s="0"/>
-      <c r="GU2" s="0" t="n">
-        <v>9.67</v>
-      </c>
+      <c r="GU2" s="0"/>
       <c r="GV2" s="0"/>
       <c r="GW2" s="0"/>
-      <c r="GX2" s="0"/>
+      <c r="GX2" s="0" t="n">
+        <v>19.9</v>
+      </c>
       <c r="GY2" s="0"/>
       <c r="GZ2" s="0"/>
       <c r="HA2" s="0"/>
       <c r="HB2" s="0"/>
-      <c r="HC2" s="0" t="n">
-        <v>6.28</v>
-      </c>
+      <c r="HC2" s="0"/>
       <c r="HD2" s="0"/>
       <c r="HE2" s="0"/>
-      <c r="HF2" s="0"/>
+      <c r="HF2" s="0" t="n">
+        <v>10.47</v>
+      </c>
       <c r="HG2" s="0"/>
-      <c r="HH2" s="0" t="n">
-        <v>22.35</v>
-      </c>
+      <c r="HH2" s="0"/>
       <c r="HI2" s="0"/>
-      <c r="HJ2" s="0" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="HK2" s="0"/>
-      <c r="HL2" s="0" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="HM2" s="0"/>
-      <c r="HN2" s="0" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="HO2" s="0"/>
-      <c r="HP2" s="0" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="HQ2" s="0"/>
-      <c r="HR2" s="0" t="n">
-        <v>34.44</v>
-      </c>
-      <c r="HS2" s="0"/>
+      <c r="HJ2" s="0"/>
+      <c r="HK2" s="0" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="HL2" s="0"/>
+      <c r="HM2" s="0" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="HN2" s="0"/>
+      <c r="HO2" s="0" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="HP2" s="0"/>
+      <c r="HQ2" s="0" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="HR2" s="0"/>
+      <c r="HS2" s="0" t="n">
+        <v>23.83</v>
+      </c>
       <c r="HT2" s="0"/>
-      <c r="HU2" s="0"/>
+      <c r="HU2" s="0" t="n">
+        <v>134.67</v>
+      </c>
       <c r="HV2" s="0"/>
       <c r="HW2" s="0"/>
       <c r="HX2" s="0"/>
@@ -2104,15 +2104,19 @@
       <c r="IM2" s="0"/>
       <c r="IN2" s="0"/>
       <c r="IO2" s="0"/>
-      <c r="IP2" s="0" t="n">
-        <v>16.87</v>
-      </c>
+      <c r="IP2" s="0"/>
       <c r="IQ2" s="0"/>
       <c r="IR2" s="0"/>
       <c r="IS2" s="0"/>
-      <c r="IT2" s="0"/>
+      <c r="IT2" s="0" t="n">
+        <v>81.52</v>
+      </c>
       <c r="IU2" s="0"/>
       <c r="IV2" s="0"/>
+      <c r="IW2" s="0"/>
+      <c r="IX2" s="0"/>
+      <c r="IY2" s="0"/>
+      <c r="IZ2" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Simulation Survey Data/results-survey581821.xlsx
+++ b/Simulation Survey Data/results-survey581821.xlsx
@@ -107,7 +107,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:IZ2"/>
+  <dimension ref="A1:KA3"/>
   <cols>
     <col collapsed="false" hidden="false" max="1024" min="1" style="0" customWidth="false" width="11.5"/>
   </cols>
@@ -140,1275 +140,1410 @@
       </c>
       <c r="F1" s="0" t="inlineStr">
         <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
           <t>startdate</t>
         </is>
       </c>
-      <c r="G1" s="0" t="inlineStr">
+      <c r="H1" s="0" t="inlineStr">
         <is>
           <t>datestamp</t>
         </is>
       </c>
-      <c r="H1" s="0" t="inlineStr">
+      <c r="I1" s="0" t="inlineStr">
         <is>
           <t>refurl</t>
         </is>
       </c>
-      <c r="I1" s="0" t="inlineStr">
+      <c r="J1" s="0" t="inlineStr">
         <is>
           <t>timePoint</t>
         </is>
       </c>
-      <c r="J1" s="0" t="inlineStr">
+      <c r="K1" s="0" t="inlineStr">
         <is>
           <t>Einv</t>
         </is>
       </c>
-      <c r="K1" s="0" t="inlineStr">
+      <c r="L1" s="0" t="inlineStr">
         <is>
           <t>randomGroup</t>
         </is>
       </c>
-      <c r="L1" s="0" t="inlineStr">
+      <c r="M1" s="0" t="inlineStr">
         <is>
           <t>studyGroup</t>
         </is>
       </c>
-      <c r="M1" s="0" t="inlineStr">
+      <c r="N1" s="0" t="inlineStr">
         <is>
           <t>AppName</t>
         </is>
       </c>
-      <c r="N1" s="0" t="inlineStr">
+      <c r="O1" s="0" t="inlineStr">
         <is>
           <t>Bew1</t>
         </is>
       </c>
-      <c r="O1" s="0" t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>Bew2</t>
         </is>
       </c>
-      <c r="P1" s="0" t="inlineStr">
+      <c r="Q1" s="0" t="inlineStr">
         <is>
           <t>Bew3</t>
         </is>
       </c>
-      <c r="Q1" s="0" t="inlineStr">
+      <c r="R1" s="0" t="inlineStr">
         <is>
           <t>Bew4</t>
         </is>
       </c>
-      <c r="R1" s="0" t="inlineStr">
+      <c r="S1" s="0" t="inlineStr">
         <is>
           <t>Bew5</t>
         </is>
       </c>
-      <c r="S1" s="0" t="inlineStr">
+      <c r="T1" s="0" t="inlineStr">
         <is>
           <t>Bew6</t>
         </is>
       </c>
-      <c r="T1" s="0" t="inlineStr">
+      <c r="U1" s="0" t="inlineStr">
         <is>
           <t>STG</t>
         </is>
       </c>
-      <c r="U1" s="0" t="inlineStr">
+      <c r="V1" s="0" t="inlineStr">
+        <is>
+          <t>METtotal</t>
+        </is>
+      </c>
+      <c r="W1" s="0" t="inlineStr">
+        <is>
+          <t>PAFlag</t>
+        </is>
+      </c>
+      <c r="X1" s="0" t="inlineStr">
+        <is>
+          <t>PASubgroup</t>
+        </is>
+      </c>
+      <c r="Y1" s="0" t="inlineStr">
         <is>
           <t>Habit[Habit1]</t>
         </is>
       </c>
-      <c r="V1" s="0" t="inlineStr">
+      <c r="Z1" s="0" t="inlineStr">
         <is>
           <t>Habit[Habit2]</t>
         </is>
       </c>
-      <c r="W1" s="0" t="inlineStr">
+      <c r="AA1" s="0" t="inlineStr">
         <is>
           <t>Habit[Habit3]</t>
         </is>
       </c>
-      <c r="X1" s="0" t="inlineStr">
+      <c r="AB1" s="0" t="inlineStr">
         <is>
           <t>Habit[Habit4]</t>
         </is>
       </c>
-      <c r="Y1" s="0" t="inlineStr">
+      <c r="AC1" s="0" t="inlineStr">
         <is>
           <t>Intention1[Int1]</t>
         </is>
       </c>
-      <c r="Z1" s="0" t="inlineStr">
+      <c r="AD1" s="0" t="inlineStr">
         <is>
           <t>Intention2[Int2]</t>
         </is>
       </c>
-      <c r="AA1" s="0" t="inlineStr">
+      <c r="AE1" s="0" t="inlineStr">
         <is>
           <t>Intention3[Int3]</t>
         </is>
       </c>
-      <c r="AB1" s="0" t="inlineStr">
+      <c r="AF1" s="0" t="inlineStr">
         <is>
           <t>Att1[Att1]</t>
         </is>
       </c>
-      <c r="AC1" s="0" t="inlineStr">
+      <c r="AG1" s="0" t="inlineStr">
         <is>
           <t>Att2[Att2]</t>
         </is>
       </c>
-      <c r="AD1" s="0" t="inlineStr">
+      <c r="AH1" s="0" t="inlineStr">
         <is>
           <t>Att3[Att3]</t>
         </is>
       </c>
-      <c r="AE1" s="0" t="inlineStr">
+      <c r="AI1" s="0" t="inlineStr">
         <is>
           <t>Att4[Att4]</t>
         </is>
       </c>
-      <c r="AF1" s="0" t="inlineStr">
+      <c r="AJ1" s="0" t="inlineStr">
         <is>
           <t>Att5[Att5]</t>
         </is>
       </c>
-      <c r="AG1" s="0" t="inlineStr">
+      <c r="AK1" s="0" t="inlineStr">
         <is>
           <t>Norm1[Norm1]</t>
         </is>
       </c>
-      <c r="AH1" s="0" t="inlineStr">
+      <c r="AL1" s="0" t="inlineStr">
         <is>
           <t>Norm2[Norm2]</t>
         </is>
       </c>
-      <c r="AI1" s="0" t="inlineStr">
+      <c r="AM1" s="0" t="inlineStr">
         <is>
           <t>Norm3[Norm3]</t>
         </is>
       </c>
-      <c r="AJ1" s="0" t="inlineStr">
+      <c r="AN1" s="0" t="inlineStr">
         <is>
           <t>ACheck1[ACheck1]</t>
         </is>
       </c>
-      <c r="AK1" s="0" t="inlineStr">
+      <c r="AO1" s="0" t="inlineStr">
         <is>
           <t>Norm4[Norm4]</t>
         </is>
       </c>
-      <c r="AL1" s="0" t="inlineStr">
+      <c r="AP1" s="0" t="inlineStr">
         <is>
           <t>Norm5[Norm5]</t>
         </is>
       </c>
-      <c r="AM1" s="0" t="inlineStr">
+      <c r="AQ1" s="0" t="inlineStr">
         <is>
           <t>Norm6[Norm6]</t>
         </is>
       </c>
-      <c r="AN1" s="0" t="inlineStr">
+      <c r="AR1" s="0" t="inlineStr">
         <is>
           <t>Control1[Con1]</t>
         </is>
       </c>
-      <c r="AO1" s="0" t="inlineStr">
+      <c r="AS1" s="0" t="inlineStr">
         <is>
           <t>Control2[Con2]</t>
         </is>
       </c>
-      <c r="AP1" s="0" t="inlineStr">
+      <c r="AT1" s="0" t="inlineStr">
         <is>
           <t>Control3[Con3]</t>
         </is>
       </c>
-      <c r="AQ1" s="0" t="inlineStr">
+      <c r="AU1" s="0" t="inlineStr">
         <is>
           <t>Control4[Con4]</t>
         </is>
       </c>
-      <c r="AR1" s="0" t="inlineStr">
+      <c r="AV1" s="0" t="inlineStr">
         <is>
           <t>KIM[IntVer1]</t>
         </is>
       </c>
-      <c r="AS1" s="0" t="inlineStr">
+      <c r="AW1" s="0" t="inlineStr">
         <is>
           <t>KIM[IntVer2]</t>
         </is>
       </c>
-      <c r="AT1" s="0" t="inlineStr">
+      <c r="AX1" s="0" t="inlineStr">
         <is>
           <t>KIM[IntVer3]</t>
         </is>
       </c>
-      <c r="AU1" s="0" t="inlineStr">
+      <c r="AY1" s="0" t="inlineStr">
         <is>
           <t>KIM[wKomp1]</t>
         </is>
       </c>
-      <c r="AV1" s="0" t="inlineStr">
+      <c r="AZ1" s="0" t="inlineStr">
         <is>
           <t>KIM[wKomp2]</t>
         </is>
       </c>
-      <c r="AW1" s="0" t="inlineStr">
+      <c r="BA1" s="0" t="inlineStr">
         <is>
           <t>KIM[wKomp3]</t>
         </is>
       </c>
-      <c r="AX1" s="0" t="inlineStr">
+      <c r="BB1" s="0" t="inlineStr">
         <is>
           <t>KIM[wWahl1]</t>
         </is>
       </c>
-      <c r="AY1" s="0" t="inlineStr">
+      <c r="BC1" s="0" t="inlineStr">
         <is>
           <t>KIM[wWahl2]</t>
         </is>
       </c>
-      <c r="AZ1" s="0" t="inlineStr">
+      <c r="BD1" s="0" t="inlineStr">
         <is>
           <t>KIM[wWahl3]</t>
         </is>
       </c>
-      <c r="BA1" s="0" t="inlineStr">
+      <c r="BE1" s="0" t="inlineStr">
         <is>
           <t>KIM[DrAn1]</t>
         </is>
       </c>
-      <c r="BB1" s="0" t="inlineStr">
+      <c r="BF1" s="0" t="inlineStr">
         <is>
           <t>KIM[DrAn2]</t>
         </is>
       </c>
-      <c r="BC1" s="0" t="inlineStr">
+      <c r="BG1" s="0" t="inlineStr">
         <is>
           <t>KIM[DrAn3]</t>
         </is>
       </c>
-      <c r="BD1" s="0" t="inlineStr">
+      <c r="BH1" s="0" t="inlineStr">
         <is>
           <t>KIM[ACheck2]</t>
         </is>
       </c>
-      <c r="BE1" s="0" t="inlineStr">
+      <c r="BI1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[discat1]</t>
         </is>
       </c>
-      <c r="BF1" s="0" t="inlineStr">
+      <c r="BJ1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[discat2]</t>
         </is>
       </c>
-      <c r="BG1" s="0" t="inlineStr">
+      <c r="BK1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[discat3]</t>
         </is>
       </c>
-      <c r="BH1" s="0" t="inlineStr">
+      <c r="BL1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[discat4]</t>
         </is>
       </c>
-      <c r="BI1" s="0" t="inlineStr">
+      <c r="BM1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[discat5]</t>
         </is>
       </c>
-      <c r="BJ1" s="0" t="inlineStr">
+      <c r="BN1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[enjoy1]</t>
         </is>
       </c>
-      <c r="BK1" s="0" t="inlineStr">
+      <c r="BO1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[enjoy2]</t>
         </is>
       </c>
-      <c r="BL1" s="0" t="inlineStr">
+      <c r="BP1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[enjoy3]</t>
         </is>
       </c>
-      <c r="BM1" s="0" t="inlineStr">
+      <c r="BQ1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[fit1]</t>
         </is>
       </c>
-      <c r="BN1" s="0" t="inlineStr">
+      <c r="BR1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[fit2]</t>
         </is>
       </c>
-      <c r="BO1" s="0" t="inlineStr">
+      <c r="BS1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[fit3]</t>
         </is>
       </c>
-      <c r="BP1" s="0" t="inlineStr">
+      <c r="BT1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[heal1]</t>
         </is>
       </c>
-      <c r="BQ1" s="0" t="inlineStr">
+      <c r="BU1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[heal2]</t>
         </is>
       </c>
-      <c r="BR1" s="0" t="inlineStr">
+      <c r="BV1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[heal3]</t>
         </is>
       </c>
-      <c r="BS1" s="0" t="inlineStr">
+      <c r="BW1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[comper1]</t>
         </is>
       </c>
-      <c r="BT1" s="0" t="inlineStr">
+      <c r="BX1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[comper2]</t>
         </is>
       </c>
-      <c r="BU1" s="0" t="inlineStr">
+      <c r="BY1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[comper3]</t>
         </is>
       </c>
-      <c r="BV1" s="0" t="inlineStr">
+      <c r="BZ1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[aes1]</t>
         </is>
       </c>
-      <c r="BW1" s="0" t="inlineStr">
+      <c r="CA1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[aes2]</t>
         </is>
       </c>
-      <c r="BX1" s="0" t="inlineStr">
+      <c r="CB1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[con1]</t>
         </is>
       </c>
-      <c r="BY1" s="0" t="inlineStr">
+      <c r="CC1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[con2]</t>
         </is>
       </c>
-      <c r="BZ1" s="0" t="inlineStr">
+      <c r="CD1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[con3]</t>
         </is>
       </c>
-      <c r="CA1" s="0" t="inlineStr">
+      <c r="CE1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[con4]</t>
         </is>
       </c>
-      <c r="CB1" s="0" t="inlineStr">
+      <c r="CF1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[con5]</t>
         </is>
       </c>
-      <c r="CC1" s="0" t="inlineStr">
+      <c r="CG1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[figapp1]</t>
         </is>
       </c>
-      <c r="CD1" s="0" t="inlineStr">
+      <c r="CH1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[figapp2]</t>
         </is>
       </c>
-      <c r="CE1" s="0" t="inlineStr">
+      <c r="CI1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[figapp3]</t>
         </is>
       </c>
-      <c r="CF1" s="0" t="inlineStr">
+      <c r="CJ1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[risk1]</t>
         </is>
       </c>
-      <c r="CG1" s="0" t="inlineStr">
+      <c r="CK1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[risk2]</t>
         </is>
       </c>
-      <c r="CH1" s="0" t="inlineStr">
+      <c r="CL1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[risk3]</t>
         </is>
       </c>
-      <c r="CI1" s="0" t="inlineStr">
+      <c r="CM1" s="0" t="inlineStr">
         <is>
           <t>ZiMo[ACheck3]</t>
         </is>
       </c>
-      <c r="CJ1" s="0" t="inlineStr">
+      <c r="CN1" s="0" t="inlineStr">
         <is>
           <t>MotivComp[MotivComp1]</t>
         </is>
       </c>
-      <c r="CK1" s="0" t="inlineStr">
+      <c r="CO1" s="0" t="inlineStr">
         <is>
           <t>MotivComp[MotivComp2]</t>
         </is>
       </c>
-      <c r="CL1" s="0" t="inlineStr">
+      <c r="CP1" s="0" t="inlineStr">
         <is>
           <t>MotivComp[MotivComp3]</t>
         </is>
       </c>
-      <c r="CM1" s="0" t="inlineStr">
+      <c r="CQ1" s="0" t="inlineStr">
         <is>
           <t>MotivComp[MotivComp4]</t>
         </is>
       </c>
-      <c r="CN1" s="0" t="inlineStr">
+      <c r="CR1" s="0" t="inlineStr">
         <is>
           <t>VolSelf[VolSelf1]</t>
         </is>
       </c>
-      <c r="CO1" s="0" t="inlineStr">
+      <c r="CS1" s="0" t="inlineStr">
         <is>
           <t>VolSelf[VolSelf2]</t>
         </is>
       </c>
-      <c r="CP1" s="0" t="inlineStr">
+      <c r="CT1" s="0" t="inlineStr">
         <is>
           <t>VolSelf[VolSelf3]</t>
         </is>
       </c>
-      <c r="CQ1" s="0" t="inlineStr">
+      <c r="CU1" s="0" t="inlineStr">
         <is>
           <t>ActionPlan[ActionPlan1]</t>
         </is>
       </c>
-      <c r="CR1" s="0" t="inlineStr">
+      <c r="CV1" s="0" t="inlineStr">
         <is>
           <t>ActionPlan[ActionPlan2]</t>
         </is>
       </c>
-      <c r="CS1" s="0" t="inlineStr">
+      <c r="CW1" s="0" t="inlineStr">
         <is>
           <t>ActionPlan[ActionPlan3]</t>
         </is>
       </c>
-      <c r="CT1" s="0" t="inlineStr">
+      <c r="CX1" s="0" t="inlineStr">
         <is>
           <t>ActionPlan[ActionPlan4]</t>
         </is>
       </c>
-      <c r="CU1" s="0" t="inlineStr">
+      <c r="CY1" s="0" t="inlineStr">
+        <is>
+          <t>AttentionCheckFlag</t>
+        </is>
+      </c>
+      <c r="CZ1" s="0" t="inlineStr">
         <is>
           <t>Geb</t>
         </is>
       </c>
-      <c r="CV1" s="0" t="inlineStr">
+      <c r="DA1" s="0" t="inlineStr">
         <is>
           <t>Ges</t>
         </is>
       </c>
-      <c r="CW1" s="0" t="inlineStr">
+      <c r="DB1" s="0" t="inlineStr">
         <is>
           <t>Ges[other]</t>
         </is>
       </c>
-      <c r="CX1" s="0" t="inlineStr">
+      <c r="DC1" s="0" t="inlineStr">
+        <is>
+          <t>Branche</t>
+        </is>
+      </c>
+      <c r="DD1" s="0" t="inlineStr">
         <is>
           <t>Ethn[Eu]</t>
         </is>
       </c>
-      <c r="CY1" s="0" t="inlineStr">
+      <c r="DE1" s="0" t="inlineStr">
         <is>
           <t>Ethn[Eucomment]</t>
         </is>
       </c>
-      <c r="CZ1" s="0" t="inlineStr">
+      <c r="DF1" s="0" t="inlineStr">
         <is>
           <t>Ethn[As]</t>
         </is>
       </c>
-      <c r="DA1" s="0" t="inlineStr">
+      <c r="DG1" s="0" t="inlineStr">
         <is>
           <t>Ethn[Ascomment]</t>
         </is>
       </c>
-      <c r="DB1" s="0" t="inlineStr">
+      <c r="DH1" s="0" t="inlineStr">
         <is>
           <t>Ethn[Am]</t>
         </is>
       </c>
-      <c r="DC1" s="0" t="inlineStr">
+      <c r="DI1" s="0" t="inlineStr">
         <is>
           <t>Ethn[Amcomment]</t>
         </is>
       </c>
-      <c r="DD1" s="0" t="inlineStr">
+      <c r="DJ1" s="0" t="inlineStr">
         <is>
           <t>Ethn[Af]</t>
         </is>
       </c>
-      <c r="DE1" s="0" t="inlineStr">
+      <c r="DK1" s="0" t="inlineStr">
         <is>
           <t>Ethn[Afcomment]</t>
         </is>
       </c>
-      <c r="DF1" s="0" t="inlineStr">
+      <c r="DL1" s="0" t="inlineStr">
         <is>
           <t>Ethn[AuNe]</t>
         </is>
       </c>
-      <c r="DG1" s="0" t="inlineStr">
+      <c r="DM1" s="0" t="inlineStr">
         <is>
           <t>Ethn[AuNecomment]</t>
         </is>
       </c>
-      <c r="DH1" s="0" t="inlineStr">
+      <c r="DN1" s="0" t="inlineStr">
         <is>
           <t>Ethn[LaAa]</t>
         </is>
       </c>
-      <c r="DI1" s="0" t="inlineStr">
+      <c r="DO1" s="0" t="inlineStr">
         <is>
           <t>Ethn[LaAacomment]</t>
         </is>
       </c>
-      <c r="DJ1" s="0" t="inlineStr">
+      <c r="DP1" s="0" t="inlineStr">
         <is>
           <t>Ethn[Noe]</t>
         </is>
       </c>
-      <c r="DK1" s="0" t="inlineStr">
+      <c r="DQ1" s="0" t="inlineStr">
         <is>
           <t>Ethn[Noecomment]</t>
         </is>
       </c>
-      <c r="DL1" s="0" t="inlineStr">
+      <c r="DR1" s="0" t="inlineStr">
         <is>
           <t>Ethn[In]</t>
         </is>
       </c>
-      <c r="DM1" s="0" t="inlineStr">
+      <c r="DS1" s="0" t="inlineStr">
         <is>
           <t>Ethn[Incomment]</t>
         </is>
       </c>
-      <c r="DN1" s="0" t="inlineStr">
+      <c r="DT1" s="0" t="inlineStr">
         <is>
           <t>Ethn[other]</t>
         </is>
       </c>
-      <c r="DO1" s="0" t="inlineStr">
+      <c r="DU1" s="0" t="inlineStr">
         <is>
           <t>Ethn[othercomment]</t>
         </is>
       </c>
-      <c r="DP1" s="0" t="inlineStr">
+      <c r="DV1" s="0" t="inlineStr">
+        <is>
+          <t>QualAppGeneral</t>
+        </is>
+      </c>
+      <c r="DW1" s="0" t="inlineStr">
+        <is>
+          <t>Edu</t>
+        </is>
+      </c>
+      <c r="DX1" s="0" t="inlineStr">
+        <is>
+          <t>Prof</t>
+        </is>
+      </c>
+      <c r="DY1" s="0" t="inlineStr">
+        <is>
+          <t>Prof[other]</t>
+        </is>
+      </c>
+      <c r="DZ1" s="0" t="inlineStr">
+        <is>
+          <t>Einko</t>
+        </is>
+      </c>
+      <c r="EA1" s="0" t="inlineStr">
+        <is>
+          <t>Einko[other]</t>
+        </is>
+      </c>
+      <c r="EB1" s="0" t="inlineStr">
+        <is>
+          <t>UmgebTyp[Ver]</t>
+        </is>
+      </c>
+      <c r="EC1" s="0" t="inlineStr">
+        <is>
+          <t>UmgebTyp[Nat]</t>
+        </is>
+      </c>
+      <c r="ED1" s="0" t="inlineStr">
+        <is>
+          <t>UmgebTyp[Mov]</t>
+        </is>
+      </c>
+      <c r="EE1" s="0" t="inlineStr">
         <is>
           <t>Wohn</t>
         </is>
       </c>
-      <c r="DQ1" s="0" t="inlineStr">
+      <c r="EF1" s="0" t="inlineStr">
         <is>
           <t>Wohn[other]</t>
         </is>
       </c>
-      <c r="DR1" s="0" t="inlineStr">
-        <is>
-          <t>Edu</t>
-        </is>
-      </c>
-      <c r="DS1" s="0" t="inlineStr">
-        <is>
-          <t>Prof</t>
-        </is>
-      </c>
-      <c r="DT1" s="0" t="inlineStr">
-        <is>
-          <t>Prof[other]</t>
-        </is>
-      </c>
-      <c r="DU1" s="0" t="inlineStr">
-        <is>
-          <t>Einko</t>
-        </is>
-      </c>
-      <c r="DV1" s="0" t="inlineStr">
-        <is>
-          <t>Einko[other]</t>
-        </is>
-      </c>
-      <c r="DW1" s="0" t="inlineStr">
-        <is>
-          <t>Branche</t>
-        </is>
-      </c>
-      <c r="DX1" s="0" t="inlineStr">
+      <c r="EG1" s="0" t="inlineStr">
+        <is>
+          <t>Wohnort</t>
+        </is>
+      </c>
+      <c r="EH1" s="0" t="inlineStr">
+        <is>
+          <t>HHGroesse</t>
+        </is>
+      </c>
+      <c r="EI1" s="0" t="inlineStr">
+        <is>
+          <t>EntfernPOI[BStel]</t>
+        </is>
+      </c>
+      <c r="EJ1" s="0" t="inlineStr">
+        <is>
+          <t>EntfernPOI[InBew]</t>
+        </is>
+      </c>
+      <c r="EK1" s="0" t="inlineStr">
+        <is>
+          <t>EntfernPOI[OutBew]</t>
+        </is>
+      </c>
+      <c r="EL1" s="0" t="inlineStr">
         <is>
           <t>AlltagAbl[AufWa]</t>
         </is>
       </c>
-      <c r="DY1" s="0" t="inlineStr">
+      <c r="EM1" s="0" t="inlineStr">
         <is>
           <t>AlltagAbl[StaProf]</t>
         </is>
       </c>
-      <c r="DZ1" s="0" t="inlineStr">
+      <c r="EN1" s="0" t="inlineStr">
         <is>
           <t>AlltagAbl[EndProf]</t>
         </is>
       </c>
-      <c r="EA1" s="0" t="inlineStr">
+      <c r="EO1" s="0" t="inlineStr">
         <is>
           <t>AlltagAbl[BettZeit]</t>
         </is>
       </c>
-      <c r="EB1" s="0" t="inlineStr">
+      <c r="EP1" s="0" t="inlineStr">
         <is>
           <t>AlltagAbl[PausDau]</t>
         </is>
       </c>
-      <c r="EC1" s="0" t="inlineStr">
+      <c r="EQ1" s="0" t="inlineStr">
         <is>
           <t>AlltagAbl[FreiDau]</t>
         </is>
       </c>
-      <c r="ED1" s="0" t="inlineStr">
-        <is>
-          <t>EntfernPOI[BStel]</t>
-        </is>
-      </c>
-      <c r="EE1" s="0" t="inlineStr">
-        <is>
-          <t>EntfernPOI[InBew]</t>
-        </is>
-      </c>
-      <c r="EF1" s="0" t="inlineStr">
-        <is>
-          <t>EntfernPOI[OutBew]</t>
-        </is>
-      </c>
-      <c r="EG1" s="0" t="inlineStr">
+      <c r="ER1" s="0" t="inlineStr">
+        <is>
+          <t>HHMinderj</t>
+        </is>
+      </c>
+      <c r="ES1" s="0" t="inlineStr">
+        <is>
+          <t>CareArbeit</t>
+        </is>
+      </c>
+      <c r="ET1" s="0" t="inlineStr">
+        <is>
+          <t>CareStunden</t>
+        </is>
+      </c>
+      <c r="EU1" s="0" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="EV1" s="0" t="inlineStr">
+        <is>
+          <t>AppUseGeneral</t>
+        </is>
+      </c>
+      <c r="EW1" s="0" t="inlineStr">
         <is>
           <t>PhoneSystem</t>
         </is>
       </c>
-      <c r="EH1" s="0" t="inlineStr">
+      <c r="EX1" s="0" t="inlineStr">
         <is>
           <t>PhoneSystem[other]</t>
         </is>
       </c>
-      <c r="EI1" s="0" t="inlineStr">
-        <is>
-          <t>AppUseGeneral</t>
-        </is>
-      </c>
-      <c r="EJ1" s="0" t="inlineStr">
-        <is>
-          <t>QualAppGeneral</t>
-        </is>
-      </c>
-      <c r="EK1" s="0" t="inlineStr">
+      <c r="EY1" s="0" t="inlineStr">
         <is>
           <t>AppUseStudy</t>
         </is>
       </c>
-      <c r="EL1" s="0" t="inlineStr">
+      <c r="EZ1" s="0" t="inlineStr">
         <is>
           <t>AppUseDays</t>
         </is>
       </c>
-      <c r="EM1" s="0" t="inlineStr">
+      <c r="FA1" s="0" t="inlineStr">
         <is>
           <t>TransferAppDetail</t>
         </is>
       </c>
-      <c r="EN1" s="0" t="inlineStr">
+      <c r="FB1" s="0" t="inlineStr">
         <is>
           <t>TAM[WA1]</t>
         </is>
       </c>
-      <c r="EO1" s="0" t="inlineStr">
+      <c r="FC1" s="0" t="inlineStr">
         <is>
           <t>TAM[WA2]</t>
         </is>
       </c>
-      <c r="EP1" s="0" t="inlineStr">
+      <c r="FD1" s="0" t="inlineStr">
         <is>
           <t>TAM[WA3]</t>
         </is>
       </c>
-      <c r="EQ1" s="0" t="inlineStr">
+      <c r="FE1" s="0" t="inlineStr">
         <is>
           <t>TAM[WN1]</t>
         </is>
       </c>
-      <c r="ER1" s="0" t="inlineStr">
+      <c r="FF1" s="0" t="inlineStr">
         <is>
           <t>TAM[WN2]</t>
         </is>
       </c>
-      <c r="ES1" s="0" t="inlineStr">
+      <c r="FG1" s="0" t="inlineStr">
         <is>
           <t>TAM[WN3]</t>
         </is>
       </c>
-      <c r="ET1" s="0" t="inlineStr">
+      <c r="FH1" s="0" t="inlineStr">
         <is>
           <t>TAM[WN4]</t>
         </is>
       </c>
-      <c r="EU1" s="0" t="inlineStr">
+      <c r="FI1" s="0" t="inlineStr">
         <is>
           <t>TAM[WB1]</t>
         </is>
       </c>
-      <c r="EV1" s="0" t="inlineStr">
+      <c r="FJ1" s="0" t="inlineStr">
         <is>
           <t>TAM[WB2]</t>
         </is>
       </c>
-      <c r="EW1" s="0" t="inlineStr">
+      <c r="FK1" s="0" t="inlineStr">
         <is>
           <t>TAM[WB3]</t>
         </is>
       </c>
-      <c r="EX1" s="0" t="inlineStr">
+      <c r="FL1" s="0" t="inlineStr">
         <is>
           <t>TAM[WB4]</t>
         </is>
       </c>
-      <c r="EY1" s="0" t="inlineStr">
+      <c r="FM1" s="0" t="inlineStr">
         <is>
           <t>TAM[WF1]</t>
         </is>
       </c>
-      <c r="EZ1" s="0" t="inlineStr">
+      <c r="FN1" s="0" t="inlineStr">
         <is>
           <t>TAM[WF2]</t>
         </is>
       </c>
-      <c r="FA1" s="0" t="inlineStr">
+      <c r="FO1" s="0" t="inlineStr">
         <is>
           <t>TAM[WF3]</t>
         </is>
       </c>
-      <c r="FB1" s="0" t="inlineStr">
+      <c r="FP1" s="0" t="inlineStr">
         <is>
           <t>TAM[WF4]</t>
         </is>
       </c>
-      <c r="FC1" s="0" t="inlineStr">
+      <c r="FQ1" s="0" t="inlineStr">
         <is>
           <t>TAM[WV1]</t>
         </is>
       </c>
-      <c r="FD1" s="0" t="inlineStr">
+      <c r="FR1" s="0" t="inlineStr">
         <is>
           <t>TAM[WV2]</t>
         </is>
       </c>
-      <c r="FE1" s="0" t="inlineStr">
+      <c r="FS1" s="0" t="inlineStr">
         <is>
           <t>TAM[WV3]</t>
         </is>
       </c>
-      <c r="FF1" s="0" t="inlineStr">
+      <c r="FT1" s="0" t="inlineStr">
         <is>
           <t>TAM[WV4]</t>
         </is>
       </c>
-      <c r="FG1" s="0" t="inlineStr">
+      <c r="FU1" s="0" t="inlineStr">
         <is>
           <t>TAM[NI1]</t>
         </is>
       </c>
-      <c r="FH1" s="0" t="inlineStr">
+      <c r="FV1" s="0" t="inlineStr">
         <is>
           <t>TAM[NI2]</t>
         </is>
       </c>
-      <c r="FI1" s="0" t="inlineStr">
+      <c r="FW1" s="0" t="inlineStr">
         <is>
           <t>TAM[NI3]</t>
         </is>
       </c>
-      <c r="FJ1" s="0" t="inlineStr">
+      <c r="FX1" s="0" t="inlineStr">
         <is>
           <t>TAM[NI4]</t>
         </is>
       </c>
-      <c r="FK1" s="0" t="inlineStr">
+      <c r="FY1" s="0" t="inlineStr">
         <is>
           <t>QualPos</t>
         </is>
       </c>
-      <c r="FL1" s="0" t="inlineStr">
+      <c r="FZ1" s="0" t="inlineStr">
         <is>
           <t>QualNeg</t>
         </is>
       </c>
-      <c r="FM1" s="0" t="inlineStr">
+      <c r="GA1" s="0" t="inlineStr">
         <is>
           <t>otherAppUse</t>
         </is>
       </c>
-      <c r="FN1" s="0" t="inlineStr">
+      <c r="GB1" s="0" t="inlineStr">
         <is>
           <t>QualOthApp</t>
         </is>
       </c>
-      <c r="FO1" s="0" t="inlineStr">
+      <c r="GC1" s="0" t="inlineStr">
         <is>
           <t>SystemLink</t>
         </is>
       </c>
-      <c r="FP1" s="0" t="inlineStr">
+      <c r="GD1" s="0" t="inlineStr">
         <is>
           <t>eMailIG</t>
         </is>
       </c>
-      <c r="FQ1" s="0" t="inlineStr">
+      <c r="GE1" s="0" t="inlineStr">
         <is>
           <t>eMailValidIG</t>
         </is>
       </c>
-      <c r="FR1" s="0" t="inlineStr">
+      <c r="GF1" s="0" t="inlineStr">
         <is>
           <t>eMailKG</t>
         </is>
       </c>
-      <c r="FS1" s="0" t="inlineStr">
+      <c r="GG1" s="0" t="inlineStr">
         <is>
           <t>eMailValidKG</t>
         </is>
       </c>
-      <c r="FT1" s="0" t="inlineStr">
+      <c r="GH1" s="0" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="FU1" s="0" t="inlineStr">
+      <c r="GI1" s="0" t="inlineStr">
         <is>
           <t>interviewtime</t>
         </is>
       </c>
-      <c r="FV1" s="0" t="inlineStr">
+      <c r="GJ1" s="0" t="inlineStr">
         <is>
           <t>groupTime19488</t>
         </is>
       </c>
-      <c r="FW1" s="0" t="inlineStr">
+      <c r="GK1" s="0" t="inlineStr">
         <is>
           <t>timePointTime</t>
         </is>
       </c>
-      <c r="FX1" s="0" t="inlineStr">
+      <c r="GL1" s="0" t="inlineStr">
         <is>
           <t>groupTime19449</t>
         </is>
       </c>
-      <c r="FY1" s="0" t="inlineStr">
+      <c r="GM1" s="0" t="inlineStr">
         <is>
           <t>EinvTime</t>
         </is>
       </c>
-      <c r="FZ1" s="0" t="inlineStr">
+      <c r="GN1" s="0" t="inlineStr">
         <is>
           <t>groupTime19489</t>
         </is>
       </c>
-      <c r="GA1" s="0" t="inlineStr">
+      <c r="GO1" s="0" t="inlineStr">
         <is>
           <t>randomGroupTime</t>
         </is>
       </c>
-      <c r="GB1" s="0" t="inlineStr">
+      <c r="GP1" s="0" t="inlineStr">
         <is>
           <t>studyGroupTime</t>
         </is>
       </c>
-      <c r="GC1" s="0" t="inlineStr">
+      <c r="GQ1" s="0" t="inlineStr">
         <is>
           <t>AppNameTime</t>
         </is>
       </c>
-      <c r="GD1" s="0" t="inlineStr">
+      <c r="GR1" s="0" t="inlineStr">
         <is>
           <t>groupTime19452</t>
         </is>
       </c>
-      <c r="GE1" s="0" t="inlineStr">
+      <c r="GS1" s="0" t="inlineStr">
         <is>
           <t>Bew1Time</t>
         </is>
       </c>
-      <c r="GF1" s="0" t="inlineStr">
+      <c r="GT1" s="0" t="inlineStr">
         <is>
           <t>Bew2Time</t>
         </is>
       </c>
-      <c r="GG1" s="0" t="inlineStr">
+      <c r="GU1" s="0" t="inlineStr">
         <is>
           <t>Bew3Time</t>
         </is>
       </c>
-      <c r="GH1" s="0" t="inlineStr">
+      <c r="GV1" s="0" t="inlineStr">
         <is>
           <t>Bew4Time</t>
         </is>
       </c>
-      <c r="GI1" s="0" t="inlineStr">
+      <c r="GW1" s="0" t="inlineStr">
         <is>
           <t>Bew5Time</t>
         </is>
       </c>
-      <c r="GJ1" s="0" t="inlineStr">
+      <c r="GX1" s="0" t="inlineStr">
         <is>
           <t>Bew6Time</t>
         </is>
       </c>
-      <c r="GK1" s="0" t="inlineStr">
+      <c r="GY1" s="0" t="inlineStr">
         <is>
           <t>STGTime</t>
         </is>
       </c>
-      <c r="GL1" s="0" t="inlineStr">
+      <c r="GZ1" s="0" t="inlineStr">
+        <is>
+          <t>groupTime20095</t>
+        </is>
+      </c>
+      <c r="HA1" s="0" t="inlineStr">
+        <is>
+          <t>METtotalTime</t>
+        </is>
+      </c>
+      <c r="HB1" s="0" t="inlineStr">
+        <is>
+          <t>PAFlagTime</t>
+        </is>
+      </c>
+      <c r="HC1" s="0" t="inlineStr">
+        <is>
+          <t>PASubgroupTime</t>
+        </is>
+      </c>
+      <c r="HD1" s="0" t="inlineStr">
         <is>
           <t>groupTime19451</t>
         </is>
       </c>
-      <c r="GM1" s="0" t="inlineStr">
+      <c r="HE1" s="0" t="inlineStr">
         <is>
           <t>HabitTime</t>
         </is>
       </c>
-      <c r="GN1" s="0" t="inlineStr">
+      <c r="HF1" s="0" t="inlineStr">
         <is>
           <t>groupTime19453</t>
         </is>
       </c>
-      <c r="GO1" s="0" t="inlineStr">
+      <c r="HG1" s="0" t="inlineStr">
         <is>
           <t>Intention1Time</t>
         </is>
       </c>
-      <c r="GP1" s="0" t="inlineStr">
+      <c r="HH1" s="0" t="inlineStr">
         <is>
           <t>Intention2Time</t>
         </is>
       </c>
-      <c r="GQ1" s="0" t="inlineStr">
+      <c r="HI1" s="0" t="inlineStr">
         <is>
           <t>Intention3Time</t>
         </is>
       </c>
-      <c r="GR1" s="0" t="inlineStr">
+      <c r="HJ1" s="0" t="inlineStr">
         <is>
           <t>groupTime19454</t>
         </is>
       </c>
-      <c r="GS1" s="0" t="inlineStr">
+      <c r="HK1" s="0" t="inlineStr">
         <is>
           <t>Att1Time</t>
         </is>
       </c>
-      <c r="GT1" s="0" t="inlineStr">
+      <c r="HL1" s="0" t="inlineStr">
         <is>
           <t>Att2Time</t>
         </is>
       </c>
-      <c r="GU1" s="0" t="inlineStr">
+      <c r="HM1" s="0" t="inlineStr">
         <is>
           <t>Att3Time</t>
         </is>
       </c>
-      <c r="GV1" s="0" t="inlineStr">
+      <c r="HN1" s="0" t="inlineStr">
         <is>
           <t>Att4Time</t>
         </is>
       </c>
-      <c r="GW1" s="0" t="inlineStr">
+      <c r="HO1" s="0" t="inlineStr">
         <is>
           <t>Att5Time</t>
         </is>
       </c>
-      <c r="GX1" s="0" t="inlineStr">
+      <c r="HP1" s="0" t="inlineStr">
         <is>
           <t>groupTime19455</t>
         </is>
       </c>
-      <c r="GY1" s="0" t="inlineStr">
+      <c r="HQ1" s="0" t="inlineStr">
         <is>
           <t>Norm1Time</t>
         </is>
       </c>
-      <c r="GZ1" s="0" t="inlineStr">
+      <c r="HR1" s="0" t="inlineStr">
         <is>
           <t>Norm2Time</t>
         </is>
       </c>
-      <c r="HA1" s="0" t="inlineStr">
+      <c r="HS1" s="0" t="inlineStr">
         <is>
           <t>Norm3Time</t>
         </is>
       </c>
-      <c r="HB1" s="0" t="inlineStr">
+      <c r="HT1" s="0" t="inlineStr">
         <is>
           <t>ACheck1Time</t>
         </is>
       </c>
-      <c r="HC1" s="0" t="inlineStr">
+      <c r="HU1" s="0" t="inlineStr">
         <is>
           <t>Norm4Time</t>
         </is>
       </c>
-      <c r="HD1" s="0" t="inlineStr">
+      <c r="HV1" s="0" t="inlineStr">
         <is>
           <t>Norm5Time</t>
         </is>
       </c>
-      <c r="HE1" s="0" t="inlineStr">
+      <c r="HW1" s="0" t="inlineStr">
         <is>
           <t>Norm6Time</t>
         </is>
       </c>
-      <c r="HF1" s="0" t="inlineStr">
+      <c r="HX1" s="0" t="inlineStr">
         <is>
           <t>groupTime19456</t>
         </is>
       </c>
-      <c r="HG1" s="0" t="inlineStr">
+      <c r="HY1" s="0" t="inlineStr">
         <is>
           <t>Control1Time</t>
         </is>
       </c>
-      <c r="HH1" s="0" t="inlineStr">
+      <c r="HZ1" s="0" t="inlineStr">
         <is>
           <t>Control2Time</t>
         </is>
       </c>
-      <c r="HI1" s="0" t="inlineStr">
+      <c r="IA1" s="0" t="inlineStr">
         <is>
           <t>Control3Time</t>
         </is>
       </c>
-      <c r="HJ1" s="0" t="inlineStr">
+      <c r="IB1" s="0" t="inlineStr">
         <is>
           <t>Control4Time</t>
         </is>
       </c>
-      <c r="HK1" s="0" t="inlineStr">
+      <c r="IC1" s="0" t="inlineStr">
         <is>
           <t>groupTime19458</t>
         </is>
       </c>
-      <c r="HL1" s="0" t="inlineStr">
+      <c r="ID1" s="0" t="inlineStr">
         <is>
           <t>KIMTime</t>
         </is>
       </c>
-      <c r="HM1" s="0" t="inlineStr">
+      <c r="IE1" s="0" t="inlineStr">
         <is>
           <t>groupTime19461</t>
         </is>
       </c>
-      <c r="HN1" s="0" t="inlineStr">
+      <c r="IF1" s="0" t="inlineStr">
         <is>
           <t>ZiMoTime</t>
         </is>
       </c>
-      <c r="HO1" s="0" t="inlineStr">
+      <c r="IG1" s="0" t="inlineStr">
         <is>
           <t>groupTime19862</t>
         </is>
       </c>
-      <c r="HP1" s="0" t="inlineStr">
+      <c r="IH1" s="0" t="inlineStr">
         <is>
           <t>MotivCompTime</t>
         </is>
       </c>
-      <c r="HQ1" s="0" t="inlineStr">
+      <c r="II1" s="0" t="inlineStr">
         <is>
           <t>groupTime19863</t>
         </is>
       </c>
-      <c r="HR1" s="0" t="inlineStr">
+      <c r="IJ1" s="0" t="inlineStr">
         <is>
           <t>VolSelfTime</t>
         </is>
       </c>
-      <c r="HS1" s="0" t="inlineStr">
+      <c r="IK1" s="0" t="inlineStr">
         <is>
           <t>groupTime19864</t>
         </is>
       </c>
-      <c r="HT1" s="0" t="inlineStr">
+      <c r="IL1" s="0" t="inlineStr">
         <is>
           <t>ActionPlanTime</t>
         </is>
       </c>
-      <c r="HU1" s="0" t="inlineStr">
+      <c r="IM1" s="0" t="inlineStr">
+        <is>
+          <t>groupTime20096</t>
+        </is>
+      </c>
+      <c r="IN1" s="0" t="inlineStr">
+        <is>
+          <t>AttentionCheckFlagTime</t>
+        </is>
+      </c>
+      <c r="IO1" s="0" t="inlineStr">
         <is>
           <t>groupTime19450</t>
         </is>
       </c>
-      <c r="HV1" s="0" t="inlineStr">
+      <c r="IP1" s="0" t="inlineStr">
         <is>
           <t>GebTime</t>
         </is>
       </c>
-      <c r="HW1" s="0" t="inlineStr">
+      <c r="IQ1" s="0" t="inlineStr">
         <is>
           <t>GesTime</t>
         </is>
       </c>
-      <c r="HX1" s="0" t="inlineStr">
+      <c r="IR1" s="0" t="inlineStr">
+        <is>
+          <t>BrancheTime</t>
+        </is>
+      </c>
+      <c r="IS1" s="0" t="inlineStr">
         <is>
           <t>EthnTime</t>
         </is>
       </c>
-      <c r="HY1" s="0" t="inlineStr">
+      <c r="IT1" s="0" t="inlineStr">
+        <is>
+          <t>QualAppGeneralTime</t>
+        </is>
+      </c>
+      <c r="IU1" s="0" t="inlineStr">
+        <is>
+          <t>EduTime</t>
+        </is>
+      </c>
+      <c r="IV1" s="0" t="inlineStr">
+        <is>
+          <t>ProfTime</t>
+        </is>
+      </c>
+      <c r="IW1" s="0" t="inlineStr">
+        <is>
+          <t>EinkoTime</t>
+        </is>
+      </c>
+      <c r="IX1" s="0" t="inlineStr">
+        <is>
+          <t>UmgebTypTime</t>
+        </is>
+      </c>
+      <c r="IY1" s="0" t="inlineStr">
         <is>
           <t>WohnTime</t>
         </is>
       </c>
-      <c r="HZ1" s="0" t="inlineStr">
-        <is>
-          <t>EduTime</t>
-        </is>
-      </c>
-      <c r="IA1" s="0" t="inlineStr">
-        <is>
-          <t>ProfTime</t>
-        </is>
-      </c>
-      <c r="IB1" s="0" t="inlineStr">
-        <is>
-          <t>EinkoTime</t>
-        </is>
-      </c>
-      <c r="IC1" s="0" t="inlineStr">
-        <is>
-          <t>BrancheTime</t>
-        </is>
-      </c>
-      <c r="ID1" s="0" t="inlineStr">
+      <c r="IZ1" s="0" t="inlineStr">
+        <is>
+          <t>WohnortTime</t>
+        </is>
+      </c>
+      <c r="JA1" s="0" t="inlineStr">
+        <is>
+          <t>HHGroesseTime</t>
+        </is>
+      </c>
+      <c r="JB1" s="0" t="inlineStr">
+        <is>
+          <t>EntfernPOITime</t>
+        </is>
+      </c>
+      <c r="JC1" s="0" t="inlineStr">
         <is>
           <t>AlltagAblTime</t>
         </is>
       </c>
-      <c r="IE1" s="0" t="inlineStr">
-        <is>
-          <t>EntfernPOITime</t>
-        </is>
-      </c>
-      <c r="IF1" s="0" t="inlineStr">
+      <c r="JD1" s="0" t="inlineStr">
+        <is>
+          <t>HHMinderjTime</t>
+        </is>
+      </c>
+      <c r="JE1" s="0" t="inlineStr">
+        <is>
+          <t>CareArbeitTime</t>
+        </is>
+      </c>
+      <c r="JF1" s="0" t="inlineStr">
+        <is>
+          <t>CareStundenTime</t>
+        </is>
+      </c>
+      <c r="JG1" s="0" t="inlineStr">
+        <is>
+          <t>SocialTime</t>
+        </is>
+      </c>
+      <c r="JH1" s="0" t="inlineStr">
+        <is>
+          <t>AppUseGeneralTime</t>
+        </is>
+      </c>
+      <c r="JI1" s="0" t="inlineStr">
         <is>
           <t>PhoneSystemTime</t>
         </is>
       </c>
-      <c r="IG1" s="0" t="inlineStr">
-        <is>
-          <t>AppUseGeneralTime</t>
-        </is>
-      </c>
-      <c r="IH1" s="0" t="inlineStr">
-        <is>
-          <t>QualAppGeneralTime</t>
-        </is>
-      </c>
-      <c r="II1" s="0" t="inlineStr">
+      <c r="JJ1" s="0" t="inlineStr">
         <is>
           <t>groupTime19487</t>
         </is>
       </c>
-      <c r="IJ1" s="0" t="inlineStr">
+      <c r="JK1" s="0" t="inlineStr">
         <is>
           <t>AppUseStudyTime</t>
         </is>
       </c>
-      <c r="IK1" s="0" t="inlineStr">
+      <c r="JL1" s="0" t="inlineStr">
         <is>
           <t>AppUseDaysTime</t>
         </is>
       </c>
-      <c r="IL1" s="0" t="inlineStr">
+      <c r="JM1" s="0" t="inlineStr">
         <is>
           <t>TransferAppDetailTime</t>
         </is>
       </c>
-      <c r="IM1" s="0" t="inlineStr">
+      <c r="JN1" s="0" t="inlineStr">
         <is>
           <t>groupTime19486</t>
         </is>
       </c>
-      <c r="IN1" s="0" t="inlineStr">
+      <c r="JO1" s="0" t="inlineStr">
         <is>
           <t>TAMTime</t>
         </is>
       </c>
-      <c r="IO1" s="0" t="inlineStr">
+      <c r="JP1" s="0" t="inlineStr">
         <is>
           <t>QualPosTime</t>
         </is>
       </c>
-      <c r="IP1" s="0" t="inlineStr">
+      <c r="JQ1" s="0" t="inlineStr">
         <is>
           <t>QualNegTime</t>
         </is>
       </c>
-      <c r="IQ1" s="0" t="inlineStr">
+      <c r="JR1" s="0" t="inlineStr">
         <is>
           <t>groupTime19491</t>
         </is>
       </c>
-      <c r="IR1" s="0" t="inlineStr">
+      <c r="JS1" s="0" t="inlineStr">
         <is>
           <t>otherAppUseTime</t>
         </is>
       </c>
-      <c r="IS1" s="0" t="inlineStr">
+      <c r="JT1" s="0" t="inlineStr">
         <is>
           <t>QualOthAppTime</t>
         </is>
       </c>
-      <c r="IT1" s="0" t="inlineStr">
+      <c r="JU1" s="0" t="inlineStr">
         <is>
           <t>groupTime19462</t>
         </is>
       </c>
-      <c r="IU1" s="0" t="inlineStr">
+      <c r="JV1" s="0" t="inlineStr">
         <is>
           <t>SystemLinkTime</t>
         </is>
       </c>
-      <c r="IV1" s="0" t="inlineStr">
+      <c r="JW1" s="0" t="inlineStr">
         <is>
           <t>eMailIGTime</t>
         </is>
       </c>
-      <c r="IW1" s="0" t="inlineStr">
+      <c r="JX1" s="0" t="inlineStr">
         <is>
           <t>eMailValidIGTime</t>
         </is>
       </c>
-      <c r="IX1" s="0" t="inlineStr">
+      <c r="JY1" s="0" t="inlineStr">
         <is>
           <t>eMailKGTime</t>
         </is>
       </c>
-      <c r="IY1" s="0" t="inlineStr">
+      <c r="JZ1" s="0" t="inlineStr">
         <is>
           <t>eMailValidKGTime</t>
         </is>
       </c>
-      <c r="IZ1" s="0" t="inlineStr">
+      <c r="KA1" s="0" t="inlineStr">
         <is>
           <t>NameTime</t>
         </is>
@@ -1416,15 +1551,15 @@
     </row>
     <row collapsed="false" customFormat="false" customHeight="false" hidden="false" ht="12.1" outlineLevel="0" r="2">
       <c r="A2" s="0" t="n">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>2026-04-09 16:11:26</t>
+          <t>2026-04-30 11:12:00</t>
         </is>
       </c>
       <c r="C2" s="0" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D2" s="0" t="inlineStr">
         <is>
@@ -1432,405 +1567,179 @@
         </is>
       </c>
       <c r="E2" s="0" t="n">
-        <v>528927893</v>
-      </c>
-      <c r="F2" s="0" t="inlineStr">
-        <is>
-          <t>2026-04-09 16:04:50</t>
-        </is>
-      </c>
+        <v>1501222237</v>
+      </c>
+      <c r="F2" s="0"/>
       <c r="G2" s="0" t="inlineStr">
         <is>
-          <t>2026-04-09 16:11:26</t>
-        </is>
-      </c>
-      <c r="H2" s="0"/>
-      <c r="I2" s="0" t="n">
+          <t>2026-04-30 11:11:00</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:12:00</t>
+        </is>
+      </c>
+      <c r="I2" s="0"/>
+      <c r="J2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="0" t="inlineStr">
+      <c r="K2" s="0" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="K2" s="0" t="n">
+      <c r="L2" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" s="0" t="inlineStr">
+        <is>
+          <t>Studien KI-App</t>
+        </is>
+      </c>
+      <c r="O2" s="0" t="inlineStr">
+        <is>
+          <t>0 Tage</t>
+        </is>
+      </c>
+      <c r="P2" s="0"/>
+      <c r="Q2" s="0" t="inlineStr">
+        <is>
+          <t>2 Tage</t>
+        </is>
+      </c>
+      <c r="R2" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="S2" s="0" t="inlineStr">
+        <is>
+          <t>0 Tage</t>
+        </is>
+      </c>
+      <c r="T2" s="0"/>
+      <c r="U2" s="0" t="inlineStr">
+        <is>
+          <t>Nein, aber ich plane in den nächsten 30 Tagen mit regelmässiger körperlicher Aktivität zu starten.</t>
+        </is>
+      </c>
+      <c r="V2" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="W2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="0" t="inlineStr">
-        <is>
-          <t>Studien KI-App</t>
-        </is>
-      </c>
-      <c r="N2" s="0" t="inlineStr">
-        <is>
-          <t>1 Tag</t>
-        </is>
-      </c>
-      <c r="O2" s="0" t="n">
-        <v>56</v>
-      </c>
-      <c r="P2" s="0" t="inlineStr">
-        <is>
-          <t>4 Tage</t>
-        </is>
-      </c>
-      <c r="Q2" s="0" t="n">
-        <v>23</v>
-      </c>
-      <c r="R2" s="0" t="inlineStr">
-        <is>
-          <t>4 Tage</t>
-        </is>
-      </c>
-      <c r="S2" s="0" t="n">
-        <v>85</v>
-      </c>
-      <c r="T2" s="0" t="inlineStr">
-        <is>
-          <t>Nein, aber ich plane in den nächsten 30 Tagen mit regelmässiger körperlicher Aktivität zu starten.</t>
-        </is>
-      </c>
-      <c r="U2" s="0" t="inlineStr">
-        <is>
-          <t>3 </t>
-        </is>
-      </c>
-      <c r="V2" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="W2" s="0" t="inlineStr">
-        <is>
-          <t>3 </t>
-        </is>
-      </c>
-      <c r="X2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y2" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z2" s="0" t="inlineStr">
-        <is>
-          <t>3 </t>
-        </is>
-      </c>
-      <c r="AA2" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC2" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE2" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF2" s="0" t="inlineStr">
-        <is>
-          <t>3 </t>
-        </is>
-      </c>
-      <c r="AG2" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH2" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI2" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ2" s="0" t="inlineStr">
-        <is>
-          <t>3 </t>
-        </is>
-      </c>
-      <c r="AK2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM2" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="AP2" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ2" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR2" s="0" t="inlineStr">
-        <is>
-          <t>4 - stimmt völlig</t>
-        </is>
-      </c>
-      <c r="AS2" s="0" t="inlineStr">
-        <is>
-          <t>2 - stimmt teils-teils</t>
-        </is>
-      </c>
-      <c r="AT2" s="0" t="inlineStr">
-        <is>
-          <t>0 - stimmt gar nicht</t>
-        </is>
-      </c>
-      <c r="AU2" s="0" t="inlineStr">
-        <is>
-          <t>2 - stimmt teils-teils</t>
-        </is>
-      </c>
-      <c r="AV2" s="0" t="inlineStr">
-        <is>
-          <t>4 - stimmt völlig</t>
-        </is>
-      </c>
-      <c r="AW2" s="0" t="inlineStr">
-        <is>
-          <t>2 - stimmt teils-teils</t>
-        </is>
-      </c>
-      <c r="AX2" s="0" t="inlineStr">
-        <is>
-          <t>2 - stimmt teils-teils</t>
-        </is>
-      </c>
-      <c r="AY2" s="0" t="inlineStr">
+      <c r="Y2" s="0"/>
+      <c r="Z2" s="0"/>
+      <c r="AA2" s="0"/>
+      <c r="AB2" s="0"/>
+      <c r="AC2" s="0"/>
+      <c r="AD2" s="0"/>
+      <c r="AE2" s="0"/>
+      <c r="AF2" s="0"/>
+      <c r="AG2" s="0"/>
+      <c r="AH2" s="0"/>
+      <c r="AI2" s="0"/>
+      <c r="AJ2" s="0"/>
+      <c r="AK2" s="0"/>
+      <c r="AL2" s="0"/>
+      <c r="AM2" s="0"/>
+      <c r="AN2" s="0"/>
+      <c r="AO2" s="0"/>
+      <c r="AP2" s="0"/>
+      <c r="AQ2" s="0"/>
+      <c r="AR2" s="0"/>
+      <c r="AS2" s="0"/>
+      <c r="AT2" s="0"/>
+      <c r="AU2" s="0"/>
+      <c r="AV2" s="0"/>
+      <c r="AW2" s="0"/>
+      <c r="AX2" s="0"/>
+      <c r="AY2" s="0"/>
+      <c r="AZ2" s="0"/>
+      <c r="BA2" s="0"/>
+      <c r="BB2" s="0"/>
+      <c r="BC2" s="0"/>
+      <c r="BD2" s="0"/>
+      <c r="BE2" s="0"/>
+      <c r="BF2" s="0"/>
+      <c r="BG2" s="0"/>
+      <c r="BH2" s="0" t="inlineStr">
         <is>
           <t>3 - stimmt ziemlich</t>
         </is>
       </c>
-      <c r="AZ2" s="0" t="inlineStr">
-        <is>
-          <t>2 - stimmt teils-teils</t>
-        </is>
-      </c>
-      <c r="BA2" s="0" t="inlineStr">
-        <is>
-          <t>2 - stimmt teils-teils</t>
-        </is>
-      </c>
-      <c r="BB2" s="0" t="inlineStr">
-        <is>
-          <t>1 - stimmt wenig</t>
-        </is>
-      </c>
-      <c r="BC2" s="0" t="inlineStr">
-        <is>
-          <t>4 - stimmt völlig</t>
-        </is>
-      </c>
-      <c r="BD2" s="0" t="inlineStr">
-        <is>
-          <t>3 - stimmt ziemlich</t>
-        </is>
-      </c>
-      <c r="BE2" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF2" s="0" t="inlineStr">
-        <is>
-          <t>4 </t>
-        </is>
-      </c>
-      <c r="BG2" s="0" t="n">
+      <c r="BI2" s="0"/>
+      <c r="BJ2" s="0"/>
+      <c r="BK2" s="0"/>
+      <c r="BL2" s="0"/>
+      <c r="BM2" s="0"/>
+      <c r="BN2" s="0"/>
+      <c r="BO2" s="0"/>
+      <c r="BP2" s="0"/>
+      <c r="BQ2" s="0"/>
+      <c r="BR2" s="0"/>
+      <c r="BS2" s="0"/>
+      <c r="BT2" s="0"/>
+      <c r="BU2" s="0"/>
+      <c r="BV2" s="0"/>
+      <c r="BW2" s="0"/>
+      <c r="BX2" s="0"/>
+      <c r="BY2" s="0"/>
+      <c r="BZ2" s="0"/>
+      <c r="CA2" s="0"/>
+      <c r="CB2" s="0"/>
+      <c r="CC2" s="0"/>
+      <c r="CD2" s="0"/>
+      <c r="CE2" s="0"/>
+      <c r="CF2" s="0"/>
+      <c r="CG2" s="0"/>
+      <c r="CH2" s="0"/>
+      <c r="CI2" s="0"/>
+      <c r="CJ2" s="0"/>
+      <c r="CK2" s="0"/>
+      <c r="CL2" s="0"/>
+      <c r="CM2" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="BH2" s="0" t="inlineStr">
-        <is>
-          <t>4 </t>
-        </is>
-      </c>
-      <c r="BI2" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ2" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="BK2" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL2" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM2" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN2" s="0" t="inlineStr">
-        <is>
-          <t>4 </t>
-        </is>
-      </c>
-      <c r="BO2" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP2" s="0" t="inlineStr">
-        <is>
-          <t>4 </t>
-        </is>
-      </c>
-      <c r="BQ2" s="0" t="inlineStr">
-        <is>
-          <t>5    ich stimme voll und ganz zu</t>
-        </is>
-      </c>
-      <c r="BR2" s="0" t="inlineStr">
-        <is>
-          <t>1    ich stimme überhaupt nicht zu</t>
-        </is>
-      </c>
-      <c r="BS2" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT2" s="0" t="inlineStr">
-        <is>
-          <t>4 </t>
-        </is>
-      </c>
-      <c r="BU2" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="BV2" s="0" t="inlineStr">
-        <is>
-          <t>5    ich stimme voll und ganz zu</t>
-        </is>
-      </c>
-      <c r="BW2" s="0" t="inlineStr">
-        <is>
-          <t>4 </t>
-        </is>
-      </c>
-      <c r="BX2" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="BY2" s="0" t="inlineStr">
-        <is>
-          <t>4 </t>
-        </is>
-      </c>
-      <c r="BZ2" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="CA2" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB2" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="CC2" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD2" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="CE2" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="CF2" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="CG2" s="0" t="inlineStr">
-        <is>
-          <t>5    ich stimme voll und ganz zu</t>
-        </is>
-      </c>
-      <c r="CH2" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="CI2" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="CJ2" s="0" t="inlineStr">
-        <is>
-          <t>3 </t>
-        </is>
-      </c>
-      <c r="CK2" s="0" t="inlineStr">
-        <is>
-          <t>1     trifft nicht zu</t>
-        </is>
-      </c>
-      <c r="CL2" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="CM2" s="0" t="inlineStr">
-        <is>
-          <t>3 </t>
-        </is>
-      </c>
-      <c r="CN2" s="0" t="inlineStr">
-        <is>
-          <t>2 </t>
-        </is>
-      </c>
-      <c r="CO2" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="CP2" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="CQ2" s="0" t="inlineStr">
-        <is>
-          <t>3 </t>
-        </is>
-      </c>
-      <c r="CR2" s="0" t="inlineStr">
-        <is>
-          <t>3 </t>
-        </is>
-      </c>
-      <c r="CS2" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="CT2" s="0" t="inlineStr">
-        <is>
-          <t>2 </t>
-        </is>
-      </c>
-      <c r="CU2" s="0" t="inlineStr">
-        <is>
-          <t>2000-03-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="CV2" s="0" t="inlineStr">
-        <is>
-          <t>Männlich</t>
-        </is>
-      </c>
+      <c r="CN2" s="0"/>
+      <c r="CO2" s="0"/>
+      <c r="CP2" s="0"/>
+      <c r="CQ2" s="0"/>
+      <c r="CR2" s="0"/>
+      <c r="CS2" s="0"/>
+      <c r="CT2" s="0"/>
+      <c r="CU2" s="0"/>
+      <c r="CV2" s="0"/>
       <c r="CW2" s="0"/>
-      <c r="CX2" s="0" t="inlineStr">
+      <c r="CX2" s="0"/>
+      <c r="CY2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ2" s="0" t="inlineStr">
+        <is>
+          <t>2008-03-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="DA2" s="0" t="inlineStr">
+        <is>
+          <t>nicht binär</t>
+        </is>
+      </c>
+      <c r="DB2" s="0"/>
+      <c r="DC2" s="0" t="inlineStr">
+        <is>
+          <t>Bergbau in der Mine</t>
+        </is>
+      </c>
+      <c r="DD2" s="0" t="inlineStr">
         <is>
           <t>Nein</t>
-        </is>
-      </c>
-      <c r="CY2" s="0"/>
-      <c r="CZ2" s="0" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="DA2" s="0"/>
-      <c r="DB2" s="0" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="DC2" s="0"/>
-      <c r="DD2" s="0" t="inlineStr">
-        <is>
-          <t>Ja</t>
         </is>
       </c>
       <c r="DE2" s="0"/>
@@ -1842,7 +1751,7 @@
       <c r="DG2" s="0"/>
       <c r="DH2" s="0" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="DI2" s="0"/>
@@ -1858,110 +1767,140 @@
         </is>
       </c>
       <c r="DM2" s="0"/>
-      <c r="DN2" s="0"/>
+      <c r="DN2" s="0" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
       <c r="DO2" s="0"/>
       <c r="DP2" s="0" t="inlineStr">
         <is>
-          <t>Schweiz</t>
+          <t>Nein</t>
         </is>
       </c>
       <c r="DQ2" s="0"/>
       <c r="DR2" s="0" t="inlineStr">
         <is>
-          <t>Gymnasium/Abitur</t>
-        </is>
-      </c>
-      <c r="DS2" s="0" t="inlineStr">
-        <is>
-          <t>Studium</t>
-        </is>
-      </c>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="DS2" s="0"/>
       <c r="DT2" s="0"/>
-      <c r="DU2" s="0" t="inlineStr">
-        <is>
-          <t>1000 - 1500 CHF</t>
-        </is>
-      </c>
+      <c r="DU2" s="0"/>
       <c r="DV2" s="0"/>
       <c r="DW2" s="0" t="inlineStr">
         <is>
-          <t>Bürojob oft sitzend</t>
+          <t>Gymnasium/Abitur</t>
         </is>
       </c>
       <c r="DX2" s="0" t="inlineStr">
         <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="DY2" s="0" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
+          <t>Selbständig</t>
+        </is>
+      </c>
+      <c r="DY2" s="0"/>
       <c r="DZ2" s="0" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="EA2" s="0" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
+          <t>3500-4000 CHF</t>
+        </is>
+      </c>
+      <c r="EA2" s="0"/>
       <c r="EB2" s="0" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>Trifft eher nicht zu</t>
         </is>
       </c>
       <c r="EC2" s="0" t="inlineStr">
         <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="ED2" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="EE2" s="0" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="EF2" s="0" t="n">
-        <v>15.25</v>
-      </c>
+          <t>Teils/teils</t>
+        </is>
+      </c>
+      <c r="ED2" s="0" t="inlineStr">
+        <is>
+          <t>Trifft eher zu</t>
+        </is>
+      </c>
+      <c r="EE2" s="0" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="EF2" s="0"/>
       <c r="EG2" s="0" t="inlineStr">
         <is>
+          <t>Kleinstadt (5.000 bis unter 20.000 Einwohner:innen)</t>
+        </is>
+      </c>
+      <c r="EH2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="EI2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="EJ2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="EK2" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="EL2" s="0" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="EM2" s="0" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="EN2" s="0" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="EO2" s="0" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="EP2" s="0" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="EQ2" s="0" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="ER2" s="0"/>
+      <c r="ES2" s="0" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="ET2" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="EU2" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="EV2" s="0" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="EW2" s="0" t="inlineStr">
+        <is>
           <t>Android</t>
         </is>
       </c>
-      <c r="EH2" s="0"/>
-      <c r="EI2" s="0" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="EJ2" s="0" t="inlineStr">
-        <is>
-          <t>Oura Ring</t>
-        </is>
-      </c>
-      <c r="EK2" s="0" t="inlineStr">
+      <c r="EX2" s="0"/>
+      <c r="EY2" s="0" t="inlineStr">
         <is>
           <t>N. v.</t>
         </is>
       </c>
-      <c r="EL2" s="0"/>
-      <c r="EM2" s="0"/>
-      <c r="EN2" s="0"/>
-      <c r="EO2" s="0"/>
-      <c r="EP2" s="0"/>
-      <c r="EQ2" s="0"/>
-      <c r="ER2" s="0"/>
-      <c r="ES2" s="0"/>
-      <c r="ET2" s="0"/>
-      <c r="EU2" s="0"/>
-      <c r="EV2" s="0"/>
-      <c r="EW2" s="0"/>
-      <c r="EX2" s="0"/>
-      <c r="EY2" s="0"/>
       <c r="EZ2" s="0"/>
       <c r="FA2" s="0"/>
       <c r="FB2" s="0"/>
@@ -1975,148 +1914,710 @@
       <c r="FJ2" s="0"/>
       <c r="FK2" s="0"/>
       <c r="FL2" s="0"/>
-      <c r="FM2" s="0" t="inlineStr">
-        <is>
-          <t>N. v.</t>
-        </is>
-      </c>
+      <c r="FM2" s="0"/>
       <c r="FN2" s="0"/>
-      <c r="FO2" s="0" t="inlineStr">
-        <is>
-          <t>if(timePoint == 1,   if(PhoneSystem == "Googl", "Android: https://play.google.com/store/apps/details?id=ai.gymian.alife",    if(PhoneSystem == "Apple", "iOS: https://apps.apple.com/ch/app/alife-dein-ki-coach/id6756587565", "Android: https://play.google.com/store/apps/details?id=ai.gymian.alife | iOS: https://apps.apple.com/ch/app/alife-dein-ki-coach/id6756587565"   )  ),   if(TOKEN:ATTRIBUTE_2 == "Googl", "Android: https://play.google.com/store/apps/details?id=ai.gymian.alife",    if(TOKEN:ATTRIBUTE_2 == "Apple", "iOS: https://apps.apple.com/ch/app/alife-dein-ki-coach/id6756587565", "Android: https://play.google.com/store/apps/details?id=ai.gymian.alife | iOS: https://apps.apple.com/ch/app/alife-dein-ki-coach/id6756587565"   )  ) )</t>
-        </is>
-      </c>
-      <c r="FP2" s="0" t="inlineStr">
-        <is>
-          <t>peter.meier@gmx.ch</t>
-        </is>
-      </c>
-      <c r="FQ2" s="0" t="inlineStr">
-        <is>
-          <t>peter.meier@gmx.ch</t>
-        </is>
-      </c>
+      <c r="FO2" s="0"/>
+      <c r="FP2" s="0"/>
+      <c r="FQ2" s="0"/>
       <c r="FR2" s="0"/>
       <c r="FS2" s="0"/>
-      <c r="FT2" s="0" t="inlineStr">
-        <is>
-          <t>peter4573x</t>
-        </is>
-      </c>
-      <c r="FU2" s="0" t="n">
-        <v>404.16</v>
-      </c>
+      <c r="FT2" s="0"/>
+      <c r="FU2" s="0"/>
       <c r="FV2" s="0"/>
       <c r="FW2" s="0"/>
-      <c r="FX2" s="0" t="n">
-        <v>6.1</v>
-      </c>
+      <c r="FX2" s="0"/>
       <c r="FY2" s="0"/>
       <c r="FZ2" s="0"/>
-      <c r="GA2" s="0"/>
+      <c r="GA2" s="0" t="inlineStr">
+        <is>
+          <t>N. v.</t>
+        </is>
+      </c>
       <c r="GB2" s="0"/>
-      <c r="GC2" s="0"/>
-      <c r="GD2" s="0" t="n">
-        <v>25.9</v>
-      </c>
+      <c r="GC2" s="0" t="inlineStr">
+        <is>
+          <t>if(timePoint == 1,   if(PhoneSystem == "Googl", "Android: https://play.google.com/store/apps/details?id=ai.gymian.alife",    if(PhoneSystem == "Apple", "iOS: https://apps.apple.com/ch/app/alife-dein-ki-coach/id6756587565", "Android: https://play.google.com/store/apps/details?id=ai.gymian.alife | iOS: https://apps.apple.com/ch/app/alife-dein-ki-coach/id6756587565"   )  ),   if(TOKEN:ATTRIBUTE_2 == "Googl", "Android: https://play.google.com/store/apps/details?id=ai.gymian.alife",    if(TOKEN:ATTRIBUTE_2 == "Apple", "iOS: https://apps.apple.com/ch/app/alife-dein-ki-coach/id6756587565", "Android: https://play.google.com/store/apps/details?id=ai.gymian.alife | iOS: https://apps.apple.com/ch/app/alife-dein-ki-coach/id6756587565"   )  ) )</t>
+        </is>
+      </c>
+      <c r="GD2" s="0"/>
       <c r="GE2" s="0"/>
-      <c r="GF2" s="0"/>
-      <c r="GG2" s="0"/>
-      <c r="GH2" s="0"/>
-      <c r="GI2" s="0"/>
+      <c r="GF2" s="0" t="inlineStr">
+        <is>
+          <t>pagroup1@test.ch</t>
+        </is>
+      </c>
+      <c r="GG2" s="0" t="inlineStr">
+        <is>
+          <t>pagroup1@test.ch</t>
+        </is>
+      </c>
+      <c r="GH2" s="0" t="inlineStr">
+        <is>
+          <t>pagroup1</t>
+        </is>
+      </c>
+      <c r="GI2" s="0" t="n">
+        <v>117.19</v>
+      </c>
       <c r="GJ2" s="0"/>
       <c r="GK2" s="0"/>
       <c r="GL2" s="0" t="n">
-        <v>7.63</v>
+        <v>3.74</v>
       </c>
       <c r="GM2" s="0"/>
-      <c r="GN2" s="0" t="n">
-        <v>15.72</v>
-      </c>
+      <c r="GN2" s="0"/>
       <c r="GO2" s="0"/>
       <c r="GP2" s="0"/>
       <c r="GQ2" s="0"/>
       <c r="GR2" s="0" t="n">
-        <v>8.61</v>
+        <v>13.35</v>
       </c>
       <c r="GS2" s="0"/>
       <c r="GT2" s="0"/>
       <c r="GU2" s="0"/>
       <c r="GV2" s="0"/>
       <c r="GW2" s="0"/>
-      <c r="GX2" s="0" t="n">
-        <v>19.9</v>
-      </c>
+      <c r="GX2" s="0"/>
       <c r="GY2" s="0"/>
       <c r="GZ2" s="0"/>
       <c r="HA2" s="0"/>
       <c r="HB2" s="0"/>
       <c r="HC2" s="0"/>
-      <c r="HD2" s="0"/>
+      <c r="HD2" s="0" t="n">
+        <v>2.89</v>
+      </c>
       <c r="HE2" s="0"/>
       <c r="HF2" s="0" t="n">
-        <v>10.47</v>
+        <v>1.22</v>
       </c>
       <c r="HG2" s="0"/>
       <c r="HH2" s="0"/>
       <c r="HI2" s="0"/>
-      <c r="HJ2" s="0"/>
-      <c r="HK2" s="0" t="n">
-        <v>22.67</v>
-      </c>
+      <c r="HJ2" s="0" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="HK2" s="0"/>
       <c r="HL2" s="0"/>
-      <c r="HM2" s="0" t="n">
-        <v>36.3</v>
-      </c>
+      <c r="HM2" s="0"/>
       <c r="HN2" s="0"/>
-      <c r="HO2" s="0" t="n">
-        <v>6.42</v>
-      </c>
-      <c r="HP2" s="0"/>
-      <c r="HQ2" s="0" t="n">
-        <v>4.42</v>
-      </c>
+      <c r="HO2" s="0"/>
+      <c r="HP2" s="0" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="HQ2" s="0"/>
       <c r="HR2" s="0"/>
-      <c r="HS2" s="0" t="n">
-        <v>23.83</v>
-      </c>
+      <c r="HS2" s="0"/>
       <c r="HT2" s="0"/>
-      <c r="HU2" s="0" t="n">
-        <v>134.67</v>
-      </c>
+      <c r="HU2" s="0"/>
       <c r="HV2" s="0"/>
       <c r="HW2" s="0"/>
-      <c r="HX2" s="0"/>
+      <c r="HX2" s="0" t="n">
+        <v>1.53</v>
+      </c>
       <c r="HY2" s="0"/>
       <c r="HZ2" s="0"/>
       <c r="IA2" s="0"/>
       <c r="IB2" s="0"/>
-      <c r="IC2" s="0"/>
+      <c r="IC2" s="0" t="n">
+        <v>4.5</v>
+      </c>
       <c r="ID2" s="0"/>
-      <c r="IE2" s="0"/>
+      <c r="IE2" s="0" t="n">
+        <v>5.23</v>
+      </c>
       <c r="IF2" s="0"/>
-      <c r="IG2" s="0"/>
+      <c r="IG2" s="0" t="n">
+        <v>1.33</v>
+      </c>
       <c r="IH2" s="0"/>
-      <c r="II2" s="0"/>
+      <c r="II2" s="0" t="n">
+        <v>3.24</v>
+      </c>
       <c r="IJ2" s="0"/>
-      <c r="IK2" s="0"/>
+      <c r="IK2" s="0" t="n">
+        <v>1.44</v>
+      </c>
       <c r="IL2" s="0"/>
       <c r="IM2" s="0"/>
       <c r="IN2" s="0"/>
-      <c r="IO2" s="0"/>
+      <c r="IO2" s="0" t="n">
+        <v>53</v>
+      </c>
       <c r="IP2" s="0"/>
       <c r="IQ2" s="0"/>
       <c r="IR2" s="0"/>
       <c r="IS2" s="0"/>
-      <c r="IT2" s="0" t="n">
-        <v>81.52</v>
-      </c>
+      <c r="IT2" s="0"/>
       <c r="IU2" s="0"/>
       <c r="IV2" s="0"/>
       <c r="IW2" s="0"/>
       <c r="IX2" s="0"/>
       <c r="IY2" s="0"/>
       <c r="IZ2" s="0"/>
+      <c r="JA2" s="0"/>
+      <c r="JB2" s="0"/>
+      <c r="JC2" s="0"/>
+      <c r="JD2" s="0"/>
+      <c r="JE2" s="0"/>
+      <c r="JF2" s="0"/>
+      <c r="JG2" s="0"/>
+      <c r="JH2" s="0"/>
+      <c r="JI2" s="0"/>
+      <c r="JJ2" s="0"/>
+      <c r="JK2" s="0"/>
+      <c r="JL2" s="0"/>
+      <c r="JM2" s="0"/>
+      <c r="JN2" s="0"/>
+      <c r="JO2" s="0"/>
+      <c r="JP2" s="0"/>
+      <c r="JQ2" s="0"/>
+      <c r="JR2" s="0"/>
+      <c r="JS2" s="0"/>
+      <c r="JT2" s="0"/>
+      <c r="JU2" s="0" t="n">
+        <v>20.18</v>
+      </c>
+      <c r="JV2" s="0"/>
+      <c r="JW2" s="0"/>
+      <c r="JX2" s="0"/>
+      <c r="JY2" s="0"/>
+      <c r="JZ2" s="0"/>
+      <c r="KA2" s="0"/>
+    </row>
+    <row collapsed="false" customFormat="false" customHeight="false" hidden="false" ht="12.1" outlineLevel="0" r="3">
+      <c r="A3" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:16:00</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>1647879420</v>
+      </c>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:14:00</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:16:00</t>
+        </is>
+      </c>
+      <c r="I3" s="0"/>
+      <c r="J3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="0" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" s="0" t="inlineStr">
+        <is>
+          <t>Studien KI-App</t>
+        </is>
+      </c>
+      <c r="O3" s="0" t="inlineStr">
+        <is>
+          <t>0 Tage</t>
+        </is>
+      </c>
+      <c r="P3" s="0"/>
+      <c r="Q3" s="0" t="inlineStr">
+        <is>
+          <t>5 Tage</t>
+        </is>
+      </c>
+      <c r="R3" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="S3" s="0" t="inlineStr">
+        <is>
+          <t>0 Tage</t>
+        </is>
+      </c>
+      <c r="T3" s="0"/>
+      <c r="U3" s="0" t="inlineStr">
+        <is>
+          <t>Nein, aber ich plane in den nächsten 30 Tagen mit regelmässiger körperlicher Aktivität zu starten.</t>
+        </is>
+      </c>
+      <c r="V3" s="0" t="n">
+        <v>750</v>
+      </c>
+      <c r="W3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y3" s="0"/>
+      <c r="Z3" s="0"/>
+      <c r="AA3" s="0"/>
+      <c r="AB3" s="0"/>
+      <c r="AC3" s="0"/>
+      <c r="AD3" s="0"/>
+      <c r="AE3" s="0"/>
+      <c r="AF3" s="0"/>
+      <c r="AG3" s="0"/>
+      <c r="AH3" s="0"/>
+      <c r="AI3" s="0"/>
+      <c r="AJ3" s="0"/>
+      <c r="AK3" s="0"/>
+      <c r="AL3" s="0"/>
+      <c r="AM3" s="0"/>
+      <c r="AN3" s="0"/>
+      <c r="AO3" s="0"/>
+      <c r="AP3" s="0"/>
+      <c r="AQ3" s="0"/>
+      <c r="AR3" s="0"/>
+      <c r="AS3" s="0"/>
+      <c r="AT3" s="0"/>
+      <c r="AU3" s="0"/>
+      <c r="AV3" s="0"/>
+      <c r="AW3" s="0"/>
+      <c r="AX3" s="0"/>
+      <c r="AY3" s="0"/>
+      <c r="AZ3" s="0"/>
+      <c r="BA3" s="0"/>
+      <c r="BB3" s="0"/>
+      <c r="BC3" s="0"/>
+      <c r="BD3" s="0"/>
+      <c r="BE3" s="0"/>
+      <c r="BF3" s="0"/>
+      <c r="BG3" s="0"/>
+      <c r="BH3" s="0" t="inlineStr">
+        <is>
+          <t>3 - stimmt ziemlich</t>
+        </is>
+      </c>
+      <c r="BI3" s="0"/>
+      <c r="BJ3" s="0"/>
+      <c r="BK3" s="0"/>
+      <c r="BL3" s="0"/>
+      <c r="BM3" s="0"/>
+      <c r="BN3" s="0"/>
+      <c r="BO3" s="0"/>
+      <c r="BP3" s="0"/>
+      <c r="BQ3" s="0"/>
+      <c r="BR3" s="0"/>
+      <c r="BS3" s="0"/>
+      <c r="BT3" s="0"/>
+      <c r="BU3" s="0"/>
+      <c r="BV3" s="0"/>
+      <c r="BW3" s="0"/>
+      <c r="BX3" s="0"/>
+      <c r="BY3" s="0"/>
+      <c r="BZ3" s="0"/>
+      <c r="CA3" s="0"/>
+      <c r="CB3" s="0"/>
+      <c r="CC3" s="0"/>
+      <c r="CD3" s="0"/>
+      <c r="CE3" s="0"/>
+      <c r="CF3" s="0"/>
+      <c r="CG3" s="0"/>
+      <c r="CH3" s="0"/>
+      <c r="CI3" s="0"/>
+      <c r="CJ3" s="0"/>
+      <c r="CK3" s="0"/>
+      <c r="CL3" s="0"/>
+      <c r="CM3" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN3" s="0"/>
+      <c r="CO3" s="0"/>
+      <c r="CP3" s="0"/>
+      <c r="CQ3" s="0"/>
+      <c r="CR3" s="0"/>
+      <c r="CS3" s="0"/>
+      <c r="CT3" s="0"/>
+      <c r="CU3" s="0"/>
+      <c r="CV3" s="0"/>
+      <c r="CW3" s="0"/>
+      <c r="CX3" s="0"/>
+      <c r="CY3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ3" s="0" t="inlineStr">
+        <is>
+          <t>2008-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="DA3" s="0" t="inlineStr">
+        <is>
+          <t>nicht binär</t>
+        </is>
+      </c>
+      <c r="DB3" s="0"/>
+      <c r="DC3" s="0" t="inlineStr">
+        <is>
+          <t>Bürojob oft am Computer</t>
+        </is>
+      </c>
+      <c r="DD3" s="0" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="DE3" s="0"/>
+      <c r="DF3" s="0" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="DG3" s="0"/>
+      <c r="DH3" s="0" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="DI3" s="0"/>
+      <c r="DJ3" s="0" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="DK3" s="0"/>
+      <c r="DL3" s="0" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="DM3" s="0"/>
+      <c r="DN3" s="0" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="DO3" s="0"/>
+      <c r="DP3" s="0" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="DQ3" s="0"/>
+      <c r="DR3" s="0" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="DS3" s="0"/>
+      <c r="DT3" s="0"/>
+      <c r="DU3" s="0"/>
+      <c r="DV3" s="0"/>
+      <c r="DW3" s="0" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="DX3" s="0" t="inlineStr">
+        <is>
+          <t>Selbständig</t>
+        </is>
+      </c>
+      <c r="DY3" s="0"/>
+      <c r="DZ3" s="0" t="inlineStr">
+        <is>
+          <t>3500-4000 CHF</t>
+        </is>
+      </c>
+      <c r="EA3" s="0"/>
+      <c r="EB3" s="0" t="inlineStr">
+        <is>
+          <t>Trifft eher nicht zu</t>
+        </is>
+      </c>
+      <c r="EC3" s="0" t="inlineStr">
+        <is>
+          <t>Trifft eher zu</t>
+        </is>
+      </c>
+      <c r="ED3" s="0" t="inlineStr">
+        <is>
+          <t>Trifft eher zu</t>
+        </is>
+      </c>
+      <c r="EE3" s="0" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="EF3" s="0"/>
+      <c r="EG3" s="0" t="inlineStr">
+        <is>
+          <t>Mittelstadt (20.000 bis unter 100.000 Einwohner:innen)</t>
+        </is>
+      </c>
+      <c r="EH3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="EI3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="EJ3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="EK3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="EL3" s="0" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="EM3" s="0" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="EN3" s="0" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="EO3" s="0" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="EP3" s="0" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="EQ3" s="0" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="ER3" s="0"/>
+      <c r="ES3" s="0" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="ET3" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="EU3" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="EV3" s="0" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="EW3" s="0" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="EX3" s="0"/>
+      <c r="EY3" s="0" t="inlineStr">
+        <is>
+          <t>N. v.</t>
+        </is>
+      </c>
+      <c r="EZ3" s="0"/>
+      <c r="FA3" s="0"/>
+      <c r="FB3" s="0"/>
+      <c r="FC3" s="0"/>
+      <c r="FD3" s="0"/>
+      <c r="FE3" s="0"/>
+      <c r="FF3" s="0"/>
+      <c r="FG3" s="0"/>
+      <c r="FH3" s="0"/>
+      <c r="FI3" s="0"/>
+      <c r="FJ3" s="0"/>
+      <c r="FK3" s="0"/>
+      <c r="FL3" s="0"/>
+      <c r="FM3" s="0"/>
+      <c r="FN3" s="0"/>
+      <c r="FO3" s="0"/>
+      <c r="FP3" s="0"/>
+      <c r="FQ3" s="0"/>
+      <c r="FR3" s="0"/>
+      <c r="FS3" s="0"/>
+      <c r="FT3" s="0"/>
+      <c r="FU3" s="0"/>
+      <c r="FV3" s="0"/>
+      <c r="FW3" s="0"/>
+      <c r="FX3" s="0"/>
+      <c r="FY3" s="0"/>
+      <c r="FZ3" s="0"/>
+      <c r="GA3" s="0" t="inlineStr">
+        <is>
+          <t>N. v.</t>
+        </is>
+      </c>
+      <c r="GB3" s="0"/>
+      <c r="GC3" s="0" t="inlineStr">
+        <is>
+          <t>if(timePoint == 1,   if(PhoneSystem == "Googl", "Android: https://play.google.com/store/apps/details?id=ai.gymian.alife",    if(PhoneSystem == "Apple", "iOS: https://apps.apple.com/ch/app/alife-dein-ki-coach/id6756587565", "Android: https://play.google.com/store/apps/details?id=ai.gymian.alife | iOS: https://apps.apple.com/ch/app/alife-dein-ki-coach/id6756587565"   )  ),   if(TOKEN:ATTRIBUTE_2 == "Googl", "Android: https://play.google.com/store/apps/details?id=ai.gymian.alife",    if(TOKEN:ATTRIBUTE_2 == "Apple", "iOS: https://apps.apple.com/ch/app/alife-dein-ki-coach/id6756587565", "Android: https://play.google.com/store/apps/details?id=ai.gymian.alife | iOS: https://apps.apple.com/ch/app/alife-dein-ki-coach/id6756587565"   )  ) )</t>
+        </is>
+      </c>
+      <c r="GD3" s="0"/>
+      <c r="GE3" s="0"/>
+      <c r="GF3" s="0" t="inlineStr">
+        <is>
+          <t>pagroup2@test.ch</t>
+        </is>
+      </c>
+      <c r="GG3" s="0" t="inlineStr">
+        <is>
+          <t>pagroup2@test.ch</t>
+        </is>
+      </c>
+      <c r="GH3" s="0" t="inlineStr">
+        <is>
+          <t>pagroup2</t>
+        </is>
+      </c>
+      <c r="GI3" s="0" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="GJ3" s="0"/>
+      <c r="GK3" s="0"/>
+      <c r="GL3" s="0" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="GM3" s="0"/>
+      <c r="GN3" s="0"/>
+      <c r="GO3" s="0"/>
+      <c r="GP3" s="0"/>
+      <c r="GQ3" s="0"/>
+      <c r="GR3" s="0" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="GS3" s="0"/>
+      <c r="GT3" s="0"/>
+      <c r="GU3" s="0"/>
+      <c r="GV3" s="0"/>
+      <c r="GW3" s="0"/>
+      <c r="GX3" s="0"/>
+      <c r="GY3" s="0"/>
+      <c r="GZ3" s="0"/>
+      <c r="HA3" s="0"/>
+      <c r="HB3" s="0"/>
+      <c r="HC3" s="0"/>
+      <c r="HD3" s="0" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="HE3" s="0"/>
+      <c r="HF3" s="0" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="HG3" s="0"/>
+      <c r="HH3" s="0"/>
+      <c r="HI3" s="0"/>
+      <c r="HJ3" s="0" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="HK3" s="0"/>
+      <c r="HL3" s="0"/>
+      <c r="HM3" s="0"/>
+      <c r="HN3" s="0"/>
+      <c r="HO3" s="0"/>
+      <c r="HP3" s="0" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="HQ3" s="0"/>
+      <c r="HR3" s="0"/>
+      <c r="HS3" s="0"/>
+      <c r="HT3" s="0"/>
+      <c r="HU3" s="0"/>
+      <c r="HV3" s="0"/>
+      <c r="HW3" s="0"/>
+      <c r="HX3" s="0" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="HY3" s="0"/>
+      <c r="HZ3" s="0"/>
+      <c r="IA3" s="0"/>
+      <c r="IB3" s="0"/>
+      <c r="IC3" s="0" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="ID3" s="0"/>
+      <c r="IE3" s="0" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="IF3" s="0"/>
+      <c r="IG3" s="0" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="IH3" s="0"/>
+      <c r="II3" s="0" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="IJ3" s="0"/>
+      <c r="IK3" s="0" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="IL3" s="0"/>
+      <c r="IM3" s="0"/>
+      <c r="IN3" s="0"/>
+      <c r="IO3" s="0" t="n">
+        <v>38.78</v>
+      </c>
+      <c r="IP3" s="0"/>
+      <c r="IQ3" s="0"/>
+      <c r="IR3" s="0"/>
+      <c r="IS3" s="0"/>
+      <c r="IT3" s="0"/>
+      <c r="IU3" s="0"/>
+      <c r="IV3" s="0"/>
+      <c r="IW3" s="0"/>
+      <c r="IX3" s="0"/>
+      <c r="IY3" s="0"/>
+      <c r="IZ3" s="0"/>
+      <c r="JA3" s="0"/>
+      <c r="JB3" s="0"/>
+      <c r="JC3" s="0"/>
+      <c r="JD3" s="0"/>
+      <c r="JE3" s="0"/>
+      <c r="JF3" s="0"/>
+      <c r="JG3" s="0"/>
+      <c r="JH3" s="0"/>
+      <c r="JI3" s="0"/>
+      <c r="JJ3" s="0"/>
+      <c r="JK3" s="0"/>
+      <c r="JL3" s="0"/>
+      <c r="JM3" s="0"/>
+      <c r="JN3" s="0"/>
+      <c r="JO3" s="0"/>
+      <c r="JP3" s="0"/>
+      <c r="JQ3" s="0"/>
+      <c r="JR3" s="0"/>
+      <c r="JS3" s="0"/>
+      <c r="JT3" s="0"/>
+      <c r="JU3" s="0" t="n">
+        <v>20.78</v>
+      </c>
+      <c r="JV3" s="0"/>
+      <c r="JW3" s="0"/>
+      <c r="JX3" s="0"/>
+      <c r="JY3" s="0"/>
+      <c r="JZ3" s="0"/>
+      <c r="KA3" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
